--- a/PLC_address.xlsx
+++ b/PLC_address.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\syafiq_suhaimi\VSC projects\CMS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7A49CDF-27B2-4AC9-8DD6-346905F63D54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA980A2F-F47E-4224-B1D6-9B4A29471ADE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{94BA1258-89D2-475F-8625-7748BD6674CA}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="611" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="621" uniqueCount="201">
   <si>
     <t>Name</t>
   </si>
@@ -624,6 +624,21 @@
   </si>
   <si>
     <t>CENTRAL_REJECT</t>
+  </si>
+  <si>
+    <t>PROD_PASS</t>
+  </si>
+  <si>
+    <t>TECH_PASS</t>
+  </si>
+  <si>
+    <t>MAIN_PASS</t>
+  </si>
+  <si>
+    <t>SAP_NO</t>
+  </si>
+  <si>
+    <t>HMI Stop Cat Color</t>
   </si>
 </sst>
 </file>
@@ -1014,7 +1029,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="101">
+  <cellXfs count="110">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1126,9 +1141,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1173,15 +1185,6 @@
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1282,6 +1285,45 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2147,16 +2189,16 @@
       </c>
     </row>
     <row r="6" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="79" t="s">
+      <c r="A6" s="75" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="80" t="s">
+      <c r="B6" s="76" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="81" t="s">
+      <c r="C6" s="77" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="82" t="s">
+      <c r="D6" s="78" t="s">
         <v>47</v>
       </c>
       <c r="E6" s="12">
@@ -2264,16 +2306,16 @@
       </c>
     </row>
     <row r="7" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="65" t="s">
+      <c r="A7" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="65" t="s">
+      <c r="B7" s="61" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="67" t="s">
+      <c r="C7" s="63" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="67" t="s">
+      <c r="D7" s="63" t="s">
         <v>47</v>
       </c>
       <c r="E7" s="1">
@@ -2381,16 +2423,16 @@
       </c>
     </row>
     <row r="8" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="64" t="s">
+      <c r="A8" s="60" t="s">
         <v>125</v>
       </c>
-      <c r="B8" s="65" t="s">
+      <c r="B8" s="61" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="66" t="s">
+      <c r="C8" s="62" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="67" t="s">
+      <c r="D8" s="63" t="s">
         <v>47</v>
       </c>
       <c r="E8" s="1">
@@ -2498,16 +2540,16 @@
       </c>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.35">
-      <c r="A9" s="64" t="s">
+      <c r="A9" s="60" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="65" t="s">
+      <c r="B9" s="61" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="66" t="s">
+      <c r="C9" s="62" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="67" t="s">
+      <c r="D9" s="63" t="s">
         <v>47</v>
       </c>
       <c r="E9" s="1">
@@ -2615,13 +2657,13 @@
       </c>
     </row>
     <row r="10" spans="1:30" x14ac:dyDescent="0.35">
-      <c r="A10" s="71" t="s">
+      <c r="A10" s="67" t="s">
         <v>83</v>
       </c>
-      <c r="B10" s="72" t="s">
+      <c r="B10" s="68" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="73" t="s">
+      <c r="C10" s="69" t="s">
         <v>18</v>
       </c>
       <c r="D10" s="1" t="s">
@@ -2744,106 +2786,106 @@
       <c r="D11" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E11" s="74">
+      <c r="E11" s="70">
         <v>530</v>
       </c>
-      <c r="F11" s="74">
+      <c r="F11" s="70">
         <f t="shared" ref="F11:AD12" si="5">SUM(E11, 500)</f>
         <v>1030</v>
       </c>
-      <c r="G11" s="74">
+      <c r="G11" s="70">
         <f t="shared" si="5"/>
         <v>1530</v>
       </c>
-      <c r="H11" s="74">
+      <c r="H11" s="70">
         <f t="shared" si="5"/>
         <v>2030</v>
       </c>
-      <c r="I11" s="74">
+      <c r="I11" s="70">
         <f t="shared" si="5"/>
         <v>2530</v>
       </c>
-      <c r="J11" s="74">
+      <c r="J11" s="70">
         <f t="shared" si="5"/>
         <v>3030</v>
       </c>
-      <c r="K11" s="74">
+      <c r="K11" s="70">
         <f t="shared" si="5"/>
         <v>3530</v>
       </c>
-      <c r="L11" s="74">
+      <c r="L11" s="70">
         <f t="shared" si="5"/>
         <v>4030</v>
       </c>
-      <c r="M11" s="74">
+      <c r="M11" s="70">
         <f t="shared" si="5"/>
         <v>4530</v>
       </c>
-      <c r="N11" s="74">
+      <c r="N11" s="70">
         <f t="shared" si="5"/>
         <v>5030</v>
       </c>
-      <c r="O11" s="74">
+      <c r="O11" s="70">
         <f t="shared" si="5"/>
         <v>5530</v>
       </c>
-      <c r="P11" s="74">
+      <c r="P11" s="70">
         <f t="shared" si="5"/>
         <v>6030</v>
       </c>
-      <c r="Q11" s="74">
+      <c r="Q11" s="70">
         <f t="shared" si="5"/>
         <v>6530</v>
       </c>
-      <c r="R11" s="74">
+      <c r="R11" s="70">
         <f t="shared" si="5"/>
         <v>7030</v>
       </c>
-      <c r="S11" s="74">
+      <c r="S11" s="70">
         <f t="shared" si="5"/>
         <v>7530</v>
       </c>
-      <c r="T11" s="92">
+      <c r="T11" s="88">
         <f t="shared" si="5"/>
         <v>8030</v>
       </c>
-      <c r="U11" s="74">
+      <c r="U11" s="70">
         <f t="shared" si="5"/>
         <v>8530</v>
       </c>
-      <c r="V11" s="74">
+      <c r="V11" s="70">
         <f t="shared" si="5"/>
         <v>9030</v>
       </c>
-      <c r="W11" s="74">
+      <c r="W11" s="70">
         <f t="shared" si="5"/>
         <v>9530</v>
       </c>
-      <c r="X11" s="74">
+      <c r="X11" s="70">
         <f t="shared" si="5"/>
         <v>10030</v>
       </c>
-      <c r="Y11" s="74">
+      <c r="Y11" s="70">
         <f t="shared" si="5"/>
         <v>10530</v>
       </c>
-      <c r="Z11" s="74">
+      <c r="Z11" s="70">
         <f t="shared" si="5"/>
         <v>11030</v>
       </c>
-      <c r="AA11" s="74">
+      <c r="AA11" s="70">
         <f t="shared" si="5"/>
         <v>11530</v>
       </c>
-      <c r="AB11" s="74">
+      <c r="AB11" s="70">
         <f t="shared" si="5"/>
         <v>12030</v>
       </c>
-      <c r="AC11" s="73">
+      <c r="AC11" s="69">
         <f t="shared" si="5"/>
         <v>12530</v>
       </c>
-      <c r="AD11" s="73">
+      <c r="AD11" s="69">
         <f t="shared" si="5"/>
         <v>13030</v>
       </c>
@@ -2852,7 +2894,7 @@
       <c r="A12" s="15" t="s">
         <v>172</v>
       </c>
-      <c r="B12" s="65" t="s">
+      <c r="B12" s="61" t="s">
         <v>13</v>
       </c>
       <c r="C12" s="16" t="s">
@@ -2861,121 +2903,121 @@
       <c r="D12" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E12" s="74">
+      <c r="E12" s="70">
         <v>532</v>
       </c>
-      <c r="F12" s="74">
+      <c r="F12" s="70">
         <f t="shared" si="5"/>
         <v>1032</v>
       </c>
-      <c r="G12" s="74">
+      <c r="G12" s="70">
         <f t="shared" si="5"/>
         <v>1532</v>
       </c>
-      <c r="H12" s="74">
+      <c r="H12" s="70">
         <f t="shared" si="5"/>
         <v>2032</v>
       </c>
-      <c r="I12" s="74">
+      <c r="I12" s="70">
         <f t="shared" si="5"/>
         <v>2532</v>
       </c>
-      <c r="J12" s="74">
+      <c r="J12" s="70">
         <f t="shared" si="5"/>
         <v>3032</v>
       </c>
-      <c r="K12" s="74">
+      <c r="K12" s="70">
         <f t="shared" si="5"/>
         <v>3532</v>
       </c>
-      <c r="L12" s="74">
+      <c r="L12" s="70">
         <f t="shared" si="5"/>
         <v>4032</v>
       </c>
-      <c r="M12" s="74">
+      <c r="M12" s="70">
         <f t="shared" si="5"/>
         <v>4532</v>
       </c>
-      <c r="N12" s="74">
+      <c r="N12" s="70">
         <f t="shared" si="5"/>
         <v>5032</v>
       </c>
-      <c r="O12" s="74">
+      <c r="O12" s="70">
         <f t="shared" si="5"/>
         <v>5532</v>
       </c>
-      <c r="P12" s="74">
+      <c r="P12" s="70">
         <f t="shared" si="5"/>
         <v>6032</v>
       </c>
-      <c r="Q12" s="74">
+      <c r="Q12" s="70">
         <f t="shared" si="5"/>
         <v>6532</v>
       </c>
-      <c r="R12" s="74">
+      <c r="R12" s="70">
         <f t="shared" si="5"/>
         <v>7032</v>
       </c>
-      <c r="S12" s="74">
+      <c r="S12" s="70">
         <f t="shared" si="5"/>
         <v>7532</v>
       </c>
-      <c r="T12" s="92">
+      <c r="T12" s="88">
         <f t="shared" si="5"/>
         <v>8032</v>
       </c>
-      <c r="U12" s="74">
+      <c r="U12" s="70">
         <f t="shared" si="5"/>
         <v>8532</v>
       </c>
-      <c r="V12" s="74">
+      <c r="V12" s="70">
         <f t="shared" si="5"/>
         <v>9032</v>
       </c>
-      <c r="W12" s="74">
+      <c r="W12" s="70">
         <f t="shared" si="5"/>
         <v>9532</v>
       </c>
-      <c r="X12" s="74">
+      <c r="X12" s="70">
         <f t="shared" si="5"/>
         <v>10032</v>
       </c>
-      <c r="Y12" s="74">
+      <c r="Y12" s="70">
         <f t="shared" si="5"/>
         <v>10532</v>
       </c>
-      <c r="Z12" s="74">
+      <c r="Z12" s="70">
         <f t="shared" si="5"/>
         <v>11032</v>
       </c>
-      <c r="AA12" s="74">
+      <c r="AA12" s="70">
         <f t="shared" si="5"/>
         <v>11532</v>
       </c>
-      <c r="AB12" s="74">
+      <c r="AB12" s="70">
         <f t="shared" si="5"/>
         <v>12032</v>
       </c>
-      <c r="AC12" s="73">
+      <c r="AC12" s="69">
         <f t="shared" si="5"/>
         <v>12532</v>
       </c>
-      <c r="AD12" s="73">
+      <c r="AD12" s="69">
         <f t="shared" si="5"/>
         <v>13032</v>
       </c>
     </row>
     <row r="13" spans="1:30" x14ac:dyDescent="0.35">
-      <c r="A13" s="64" t="s">
+      <c r="A13" s="60" t="s">
         <v>84</v>
       </c>
-      <c r="B13" s="65" t="s">
+      <c r="B13" s="61" t="s">
         <v>13</v>
       </c>
-      <c r="C13" s="66" t="s">
+      <c r="C13" s="62" t="s">
         <v>18</v>
       </c>
-      <c r="D13" s="67"/>
+      <c r="D13" s="63"/>
       <c r="E13" s="1">
         <v>540</v>
       </c>
@@ -3081,16 +3123,16 @@
       </c>
     </row>
     <row r="14" spans="1:30" x14ac:dyDescent="0.35">
-      <c r="A14" s="64" t="s">
+      <c r="A14" s="60" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="65" t="s">
+      <c r="B14" s="61" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="66" t="s">
+      <c r="C14" s="62" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="67"/>
+      <c r="D14" s="63"/>
       <c r="E14" s="1">
         <v>550</v>
       </c>
@@ -3208,121 +3250,121 @@
       <c r="D15" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E15" s="74">
+      <c r="E15" s="70">
         <v>560</v>
       </c>
-      <c r="F15" s="74">
+      <c r="F15" s="70">
         <f t="shared" ref="F15:AD15" si="8">SUM(E15, 500)</f>
         <v>1060</v>
       </c>
-      <c r="G15" s="74">
+      <c r="G15" s="70">
         <f t="shared" si="8"/>
         <v>1560</v>
       </c>
-      <c r="H15" s="74">
+      <c r="H15" s="70">
         <f t="shared" si="8"/>
         <v>2060</v>
       </c>
-      <c r="I15" s="74">
+      <c r="I15" s="70">
         <f t="shared" si="8"/>
         <v>2560</v>
       </c>
-      <c r="J15" s="74">
+      <c r="J15" s="70">
         <f t="shared" si="8"/>
         <v>3060</v>
       </c>
-      <c r="K15" s="74">
+      <c r="K15" s="70">
         <f t="shared" si="8"/>
         <v>3560</v>
       </c>
-      <c r="L15" s="74">
+      <c r="L15" s="70">
         <f t="shared" si="8"/>
         <v>4060</v>
       </c>
-      <c r="M15" s="74">
+      <c r="M15" s="70">
         <f t="shared" si="8"/>
         <v>4560</v>
       </c>
-      <c r="N15" s="74">
+      <c r="N15" s="70">
         <f t="shared" si="8"/>
         <v>5060</v>
       </c>
-      <c r="O15" s="74">
+      <c r="O15" s="70">
         <f t="shared" si="8"/>
         <v>5560</v>
       </c>
-      <c r="P15" s="74">
+      <c r="P15" s="70">
         <f t="shared" si="8"/>
         <v>6060</v>
       </c>
-      <c r="Q15" s="74">
+      <c r="Q15" s="70">
         <f t="shared" si="8"/>
         <v>6560</v>
       </c>
-      <c r="R15" s="74">
+      <c r="R15" s="70">
         <f t="shared" si="8"/>
         <v>7060</v>
       </c>
-      <c r="S15" s="74">
+      <c r="S15" s="70">
         <f t="shared" si="8"/>
         <v>7560</v>
       </c>
-      <c r="T15" s="92">
+      <c r="T15" s="88">
         <f t="shared" si="8"/>
         <v>8060</v>
       </c>
-      <c r="U15" s="74">
+      <c r="U15" s="70">
         <f t="shared" si="8"/>
         <v>8560</v>
       </c>
-      <c r="V15" s="74">
+      <c r="V15" s="70">
         <f t="shared" si="8"/>
         <v>9060</v>
       </c>
-      <c r="W15" s="74">
+      <c r="W15" s="70">
         <f t="shared" si="8"/>
         <v>9560</v>
       </c>
-      <c r="X15" s="74">
+      <c r="X15" s="70">
         <f t="shared" si="8"/>
         <v>10060</v>
       </c>
-      <c r="Y15" s="74">
+      <c r="Y15" s="70">
         <f t="shared" si="8"/>
         <v>10560</v>
       </c>
-      <c r="Z15" s="74">
+      <c r="Z15" s="70">
         <f t="shared" si="8"/>
         <v>11060</v>
       </c>
-      <c r="AA15" s="74">
+      <c r="AA15" s="70">
         <f t="shared" si="8"/>
         <v>11560</v>
       </c>
-      <c r="AB15" s="74">
+      <c r="AB15" s="70">
         <f t="shared" si="8"/>
         <v>12060</v>
       </c>
-      <c r="AC15" s="73">
+      <c r="AC15" s="69">
         <f t="shared" si="8"/>
         <v>12560</v>
       </c>
-      <c r="AD15" s="73">
+      <c r="AD15" s="69">
         <f t="shared" si="8"/>
         <v>13060</v>
       </c>
     </row>
     <row r="16" spans="1:30" x14ac:dyDescent="0.35">
-      <c r="A16" s="64" t="s">
+      <c r="A16" s="60" t="s">
         <v>5</v>
       </c>
-      <c r="B16" s="65" t="s">
+      <c r="B16" s="61" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="66" t="s">
+      <c r="C16" s="62" t="s">
         <v>18</v>
       </c>
-      <c r="D16" s="67" t="s">
+      <c r="D16" s="63" t="s">
         <v>47</v>
       </c>
       <c r="E16" s="1">
@@ -3430,16 +3472,16 @@
       </c>
     </row>
     <row r="17" spans="1:30" x14ac:dyDescent="0.35">
-      <c r="A17" s="64" t="s">
+      <c r="A17" s="60" t="s">
         <v>81</v>
       </c>
-      <c r="B17" s="65" t="s">
+      <c r="B17" s="61" t="s">
         <v>13</v>
       </c>
-      <c r="C17" s="66" t="s">
+      <c r="C17" s="62" t="s">
         <v>18</v>
       </c>
-      <c r="D17" s="67" t="s">
+      <c r="D17" s="63" t="s">
         <v>48</v>
       </c>
       <c r="E17" s="1">
@@ -3559,121 +3601,121 @@
       <c r="D18" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E18" s="74">
+      <c r="E18" s="70">
         <v>590</v>
       </c>
-      <c r="F18" s="74">
+      <c r="F18" s="70">
         <f t="shared" si="10"/>
         <v>1090</v>
       </c>
-      <c r="G18" s="74">
+      <c r="G18" s="70">
         <f t="shared" si="10"/>
         <v>1590</v>
       </c>
-      <c r="H18" s="74">
+      <c r="H18" s="70">
         <f t="shared" si="10"/>
         <v>2090</v>
       </c>
-      <c r="I18" s="74">
+      <c r="I18" s="70">
         <f t="shared" si="10"/>
         <v>2590</v>
       </c>
-      <c r="J18" s="74">
+      <c r="J18" s="70">
         <f t="shared" si="10"/>
         <v>3090</v>
       </c>
-      <c r="K18" s="74">
+      <c r="K18" s="70">
         <f t="shared" si="10"/>
         <v>3590</v>
       </c>
-      <c r="L18" s="74">
+      <c r="L18" s="70">
         <f t="shared" si="10"/>
         <v>4090</v>
       </c>
-      <c r="M18" s="74">
+      <c r="M18" s="70">
         <f t="shared" si="10"/>
         <v>4590</v>
       </c>
-      <c r="N18" s="74">
+      <c r="N18" s="70">
         <f t="shared" si="10"/>
         <v>5090</v>
       </c>
-      <c r="O18" s="74">
+      <c r="O18" s="70">
         <f t="shared" si="10"/>
         <v>5590</v>
       </c>
-      <c r="P18" s="74">
+      <c r="P18" s="70">
         <f t="shared" si="10"/>
         <v>6090</v>
       </c>
-      <c r="Q18" s="74">
+      <c r="Q18" s="70">
         <f t="shared" si="10"/>
         <v>6590</v>
       </c>
-      <c r="R18" s="74">
+      <c r="R18" s="70">
         <f t="shared" si="10"/>
         <v>7090</v>
       </c>
-      <c r="S18" s="74">
+      <c r="S18" s="70">
         <f t="shared" si="10"/>
         <v>7590</v>
       </c>
-      <c r="T18" s="92">
+      <c r="T18" s="88">
         <f t="shared" si="10"/>
         <v>8090</v>
       </c>
-      <c r="U18" s="74">
+      <c r="U18" s="70">
         <f t="shared" si="10"/>
         <v>8590</v>
       </c>
-      <c r="V18" s="74">
+      <c r="V18" s="70">
         <f t="shared" si="10"/>
         <v>9090</v>
       </c>
-      <c r="W18" s="74">
+      <c r="W18" s="70">
         <f t="shared" si="10"/>
         <v>9590</v>
       </c>
-      <c r="X18" s="74">
+      <c r="X18" s="70">
         <f t="shared" si="10"/>
         <v>10090</v>
       </c>
-      <c r="Y18" s="74">
+      <c r="Y18" s="70">
         <f t="shared" si="10"/>
         <v>10590</v>
       </c>
-      <c r="Z18" s="74">
+      <c r="Z18" s="70">
         <f t="shared" si="10"/>
         <v>11090</v>
       </c>
-      <c r="AA18" s="74">
+      <c r="AA18" s="70">
         <f t="shared" si="10"/>
         <v>11590</v>
       </c>
-      <c r="AB18" s="74">
+      <c r="AB18" s="70">
         <f t="shared" si="10"/>
         <v>12090</v>
       </c>
-      <c r="AC18" s="73">
+      <c r="AC18" s="69">
         <f t="shared" si="10"/>
         <v>12590</v>
       </c>
-      <c r="AD18" s="73">
+      <c r="AD18" s="69">
         <f t="shared" si="10"/>
         <v>13090</v>
       </c>
     </row>
     <row r="19" spans="1:30" x14ac:dyDescent="0.35">
-      <c r="A19" s="71" t="s">
+      <c r="A19" s="67" t="s">
         <v>6</v>
       </c>
-      <c r="B19" s="72" t="s">
+      <c r="B19" s="68" t="s">
         <v>15</v>
       </c>
-      <c r="C19" s="73" t="s">
+      <c r="C19" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="D19" s="74" t="s">
+      <c r="D19" s="70" t="s">
         <v>47</v>
       </c>
       <c r="E19" s="1">
@@ -3781,16 +3823,16 @@
       </c>
     </row>
     <row r="20" spans="1:30" x14ac:dyDescent="0.35">
-      <c r="A20" s="71" t="s">
+      <c r="A20" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="B20" s="72" t="s">
+      <c r="B20" s="68" t="s">
         <v>15</v>
       </c>
-      <c r="C20" s="73" t="s">
+      <c r="C20" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="D20" s="74" t="s">
+      <c r="D20" s="70" t="s">
         <v>47</v>
       </c>
       <c r="E20" s="1">
@@ -3910,106 +3952,106 @@
       <c r="D21" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E21" s="74">
+      <c r="E21" s="70">
         <v>800</v>
       </c>
-      <c r="F21" s="74">
+      <c r="F21" s="70">
         <f t="shared" si="12"/>
         <v>1300</v>
       </c>
-      <c r="G21" s="74">
+      <c r="G21" s="70">
         <f t="shared" si="12"/>
         <v>1800</v>
       </c>
-      <c r="H21" s="74">
+      <c r="H21" s="70">
         <f t="shared" si="12"/>
         <v>2300</v>
       </c>
-      <c r="I21" s="74">
+      <c r="I21" s="70">
         <f t="shared" si="12"/>
         <v>2800</v>
       </c>
-      <c r="J21" s="74">
+      <c r="J21" s="70">
         <f t="shared" si="12"/>
         <v>3300</v>
       </c>
-      <c r="K21" s="74">
+      <c r="K21" s="70">
         <f t="shared" si="12"/>
         <v>3800</v>
       </c>
-      <c r="L21" s="74">
+      <c r="L21" s="70">
         <f t="shared" si="12"/>
         <v>4300</v>
       </c>
-      <c r="M21" s="74">
+      <c r="M21" s="70">
         <f t="shared" si="12"/>
         <v>4800</v>
       </c>
-      <c r="N21" s="74">
+      <c r="N21" s="70">
         <f t="shared" si="12"/>
         <v>5300</v>
       </c>
-      <c r="O21" s="74">
+      <c r="O21" s="70">
         <f t="shared" si="12"/>
         <v>5800</v>
       </c>
-      <c r="P21" s="74">
+      <c r="P21" s="70">
         <f t="shared" si="12"/>
         <v>6300</v>
       </c>
-      <c r="Q21" s="74">
+      <c r="Q21" s="70">
         <f t="shared" si="12"/>
         <v>6800</v>
       </c>
-      <c r="R21" s="74">
+      <c r="R21" s="70">
         <f t="shared" si="12"/>
         <v>7300</v>
       </c>
-      <c r="S21" s="74">
+      <c r="S21" s="70">
         <f t="shared" si="12"/>
         <v>7800</v>
       </c>
-      <c r="T21" s="92">
+      <c r="T21" s="88">
         <f t="shared" si="12"/>
         <v>8300</v>
       </c>
-      <c r="U21" s="74">
+      <c r="U21" s="70">
         <f t="shared" si="12"/>
         <v>8800</v>
       </c>
-      <c r="V21" s="74">
+      <c r="V21" s="70">
         <f t="shared" si="12"/>
         <v>9300</v>
       </c>
-      <c r="W21" s="74">
+      <c r="W21" s="70">
         <f t="shared" si="12"/>
         <v>9800</v>
       </c>
-      <c r="X21" s="74">
+      <c r="X21" s="70">
         <f t="shared" si="12"/>
         <v>10300</v>
       </c>
-      <c r="Y21" s="74">
+      <c r="Y21" s="70">
         <f t="shared" si="12"/>
         <v>10800</v>
       </c>
-      <c r="Z21" s="74">
+      <c r="Z21" s="70">
         <f t="shared" si="12"/>
         <v>11300</v>
       </c>
-      <c r="AA21" s="74">
+      <c r="AA21" s="70">
         <f t="shared" si="12"/>
         <v>11800</v>
       </c>
-      <c r="AB21" s="74">
+      <c r="AB21" s="70">
         <f t="shared" si="12"/>
         <v>12300</v>
       </c>
-      <c r="AC21" s="73">
+      <c r="AC21" s="69">
         <f t="shared" si="12"/>
         <v>12800</v>
       </c>
-      <c r="AD21" s="73">
+      <c r="AD21" s="69">
         <f t="shared" si="12"/>
         <v>13300</v>
       </c>
@@ -4027,106 +4069,106 @@
       <c r="D22" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E22" s="74">
+      <c r="E22" s="70">
         <v>900</v>
       </c>
-      <c r="F22" s="74">
+      <c r="F22" s="70">
         <f t="shared" si="12"/>
         <v>1400</v>
       </c>
-      <c r="G22" s="74">
+      <c r="G22" s="70">
         <f t="shared" si="12"/>
         <v>1900</v>
       </c>
-      <c r="H22" s="74">
+      <c r="H22" s="70">
         <f t="shared" si="12"/>
         <v>2400</v>
       </c>
-      <c r="I22" s="74">
+      <c r="I22" s="70">
         <f t="shared" si="12"/>
         <v>2900</v>
       </c>
-      <c r="J22" s="74">
+      <c r="J22" s="70">
         <f t="shared" si="12"/>
         <v>3400</v>
       </c>
-      <c r="K22" s="74">
+      <c r="K22" s="70">
         <f t="shared" si="12"/>
         <v>3900</v>
       </c>
-      <c r="L22" s="74">
+      <c r="L22" s="70">
         <f t="shared" si="12"/>
         <v>4400</v>
       </c>
-      <c r="M22" s="74">
+      <c r="M22" s="70">
         <f t="shared" si="12"/>
         <v>4900</v>
       </c>
-      <c r="N22" s="74">
+      <c r="N22" s="70">
         <f t="shared" si="12"/>
         <v>5400</v>
       </c>
-      <c r="O22" s="74">
+      <c r="O22" s="70">
         <f t="shared" si="12"/>
         <v>5900</v>
       </c>
-      <c r="P22" s="74">
+      <c r="P22" s="70">
         <f t="shared" si="12"/>
         <v>6400</v>
       </c>
-      <c r="Q22" s="74">
+      <c r="Q22" s="70">
         <f t="shared" si="12"/>
         <v>6900</v>
       </c>
-      <c r="R22" s="74">
+      <c r="R22" s="70">
         <f t="shared" si="12"/>
         <v>7400</v>
       </c>
-      <c r="S22" s="74">
+      <c r="S22" s="70">
         <f t="shared" si="12"/>
         <v>7900</v>
       </c>
-      <c r="T22" s="92">
+      <c r="T22" s="88">
         <f t="shared" si="12"/>
         <v>8400</v>
       </c>
-      <c r="U22" s="74">
+      <c r="U22" s="70">
         <f t="shared" si="12"/>
         <v>8900</v>
       </c>
-      <c r="V22" s="74">
+      <c r="V22" s="70">
         <f t="shared" si="12"/>
         <v>9400</v>
       </c>
-      <c r="W22" s="74">
+      <c r="W22" s="70">
         <f t="shared" si="12"/>
         <v>9900</v>
       </c>
-      <c r="X22" s="74">
+      <c r="X22" s="70">
         <f t="shared" si="12"/>
         <v>10400</v>
       </c>
-      <c r="Y22" s="74">
+      <c r="Y22" s="70">
         <f t="shared" si="12"/>
         <v>10900</v>
       </c>
-      <c r="Z22" s="74">
+      <c r="Z22" s="70">
         <f t="shared" si="12"/>
         <v>11400</v>
       </c>
-      <c r="AA22" s="74">
+      <c r="AA22" s="70">
         <f t="shared" si="12"/>
         <v>11900</v>
       </c>
-      <c r="AB22" s="74">
+      <c r="AB22" s="70">
         <f t="shared" si="12"/>
         <v>12400</v>
       </c>
-      <c r="AC22" s="73">
+      <c r="AC22" s="69">
         <f t="shared" si="12"/>
         <v>12900</v>
       </c>
-      <c r="AD22" s="73">
+      <c r="AD22" s="69">
         <f t="shared" si="12"/>
         <v>13400</v>
       </c>
@@ -4141,106 +4183,106 @@
       <c r="C23" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="E23" s="74">
+      <c r="E23" s="70">
         <v>750</v>
       </c>
-      <c r="F23" s="74">
+      <c r="F23" s="70">
         <f t="shared" si="12"/>
         <v>1250</v>
       </c>
-      <c r="G23" s="74">
+      <c r="G23" s="70">
         <f t="shared" si="12"/>
         <v>1750</v>
       </c>
-      <c r="H23" s="74">
+      <c r="H23" s="70">
         <f t="shared" si="12"/>
         <v>2250</v>
       </c>
-      <c r="I23" s="74">
+      <c r="I23" s="70">
         <f t="shared" si="12"/>
         <v>2750</v>
       </c>
-      <c r="J23" s="74">
+      <c r="J23" s="70">
         <f t="shared" si="12"/>
         <v>3250</v>
       </c>
-      <c r="K23" s="74">
+      <c r="K23" s="70">
         <f t="shared" si="12"/>
         <v>3750</v>
       </c>
-      <c r="L23" s="74">
+      <c r="L23" s="70">
         <f t="shared" si="12"/>
         <v>4250</v>
       </c>
-      <c r="M23" s="74">
+      <c r="M23" s="70">
         <f t="shared" si="12"/>
         <v>4750</v>
       </c>
-      <c r="N23" s="74">
+      <c r="N23" s="70">
         <f t="shared" si="12"/>
         <v>5250</v>
       </c>
-      <c r="O23" s="74">
+      <c r="O23" s="70">
         <f t="shared" si="12"/>
         <v>5750</v>
       </c>
-      <c r="P23" s="74">
+      <c r="P23" s="70">
         <f t="shared" si="12"/>
         <v>6250</v>
       </c>
-      <c r="Q23" s="74">
+      <c r="Q23" s="70">
         <f t="shared" si="12"/>
         <v>6750</v>
       </c>
-      <c r="R23" s="74">
+      <c r="R23" s="70">
         <f t="shared" si="12"/>
         <v>7250</v>
       </c>
-      <c r="S23" s="74">
+      <c r="S23" s="70">
         <f t="shared" si="12"/>
         <v>7750</v>
       </c>
-      <c r="T23" s="92">
+      <c r="T23" s="88">
         <f t="shared" si="12"/>
         <v>8250</v>
       </c>
-      <c r="U23" s="74">
+      <c r="U23" s="70">
         <f t="shared" si="12"/>
         <v>8750</v>
       </c>
-      <c r="V23" s="74">
+      <c r="V23" s="70">
         <f t="shared" si="12"/>
         <v>9250</v>
       </c>
-      <c r="W23" s="74">
+      <c r="W23" s="70">
         <f t="shared" si="12"/>
         <v>9750</v>
       </c>
-      <c r="X23" s="74">
+      <c r="X23" s="70">
         <f t="shared" si="12"/>
         <v>10250</v>
       </c>
-      <c r="Y23" s="74">
+      <c r="Y23" s="70">
         <f t="shared" si="12"/>
         <v>10750</v>
       </c>
-      <c r="Z23" s="74">
+      <c r="Z23" s="70">
         <f t="shared" si="12"/>
         <v>11250</v>
       </c>
-      <c r="AA23" s="74">
+      <c r="AA23" s="70">
         <f t="shared" si="12"/>
         <v>11750</v>
       </c>
-      <c r="AB23" s="74">
+      <c r="AB23" s="70">
         <f t="shared" si="12"/>
         <v>12250</v>
       </c>
-      <c r="AC23" s="73">
+      <c r="AC23" s="69">
         <f t="shared" si="12"/>
         <v>12750</v>
       </c>
-      <c r="AD23" s="73">
+      <c r="AD23" s="69">
         <f t="shared" si="12"/>
         <v>13250</v>
       </c>
@@ -4255,106 +4297,106 @@
       <c r="C24" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="E24" s="74">
+      <c r="E24" s="70">
         <v>755</v>
       </c>
-      <c r="F24" s="74">
+      <c r="F24" s="70">
         <f t="shared" si="12"/>
         <v>1255</v>
       </c>
-      <c r="G24" s="74">
+      <c r="G24" s="70">
         <f t="shared" si="12"/>
         <v>1755</v>
       </c>
-      <c r="H24" s="74">
+      <c r="H24" s="70">
         <f t="shared" si="12"/>
         <v>2255</v>
       </c>
-      <c r="I24" s="74">
+      <c r="I24" s="70">
         <f t="shared" si="12"/>
         <v>2755</v>
       </c>
-      <c r="J24" s="74">
+      <c r="J24" s="70">
         <f t="shared" si="12"/>
         <v>3255</v>
       </c>
-      <c r="K24" s="74">
+      <c r="K24" s="70">
         <f t="shared" si="12"/>
         <v>3755</v>
       </c>
-      <c r="L24" s="74">
+      <c r="L24" s="70">
         <f t="shared" si="12"/>
         <v>4255</v>
       </c>
-      <c r="M24" s="74">
+      <c r="M24" s="70">
         <f t="shared" si="12"/>
         <v>4755</v>
       </c>
-      <c r="N24" s="74">
+      <c r="N24" s="70">
         <f t="shared" si="12"/>
         <v>5255</v>
       </c>
-      <c r="O24" s="74">
+      <c r="O24" s="70">
         <f t="shared" si="12"/>
         <v>5755</v>
       </c>
-      <c r="P24" s="74">
+      <c r="P24" s="70">
         <f t="shared" si="12"/>
         <v>6255</v>
       </c>
-      <c r="Q24" s="74">
+      <c r="Q24" s="70">
         <f t="shared" si="12"/>
         <v>6755</v>
       </c>
-      <c r="R24" s="74">
+      <c r="R24" s="70">
         <f t="shared" si="12"/>
         <v>7255</v>
       </c>
-      <c r="S24" s="74">
+      <c r="S24" s="70">
         <f t="shared" si="12"/>
         <v>7755</v>
       </c>
-      <c r="T24" s="92">
+      <c r="T24" s="88">
         <f t="shared" si="12"/>
         <v>8255</v>
       </c>
-      <c r="U24" s="74">
+      <c r="U24" s="70">
         <f t="shared" si="12"/>
         <v>8755</v>
       </c>
-      <c r="V24" s="74">
+      <c r="V24" s="70">
         <f t="shared" si="12"/>
         <v>9255</v>
       </c>
-      <c r="W24" s="74">
+      <c r="W24" s="70">
         <f t="shared" si="12"/>
         <v>9755</v>
       </c>
-      <c r="X24" s="74">
+      <c r="X24" s="70">
         <f t="shared" si="12"/>
         <v>10255</v>
       </c>
-      <c r="Y24" s="74">
+      <c r="Y24" s="70">
         <f t="shared" si="12"/>
         <v>10755</v>
       </c>
-      <c r="Z24" s="74">
+      <c r="Z24" s="70">
         <f t="shared" si="12"/>
         <v>11255</v>
       </c>
-      <c r="AA24" s="74">
+      <c r="AA24" s="70">
         <f t="shared" si="12"/>
         <v>11755</v>
       </c>
-      <c r="AB24" s="74">
+      <c r="AB24" s="70">
         <f t="shared" si="12"/>
         <v>12255</v>
       </c>
-      <c r="AC24" s="73">
+      <c r="AC24" s="69">
         <f t="shared" si="12"/>
         <v>12755</v>
       </c>
-      <c r="AD24" s="73">
+      <c r="AD24" s="69">
         <f t="shared" si="12"/>
         <v>13255</v>
       </c>
@@ -4369,106 +4411,106 @@
       <c r="C25" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="E25" s="74">
+      <c r="E25" s="70">
         <v>760</v>
       </c>
-      <c r="F25" s="74">
+      <c r="F25" s="70">
         <f t="shared" si="12"/>
         <v>1260</v>
       </c>
-      <c r="G25" s="74">
+      <c r="G25" s="70">
         <f t="shared" si="12"/>
         <v>1760</v>
       </c>
-      <c r="H25" s="74">
+      <c r="H25" s="70">
         <f t="shared" si="12"/>
         <v>2260</v>
       </c>
-      <c r="I25" s="74">
+      <c r="I25" s="70">
         <f t="shared" si="12"/>
         <v>2760</v>
       </c>
-      <c r="J25" s="74">
+      <c r="J25" s="70">
         <f t="shared" si="12"/>
         <v>3260</v>
       </c>
-      <c r="K25" s="74">
+      <c r="K25" s="70">
         <f t="shared" si="12"/>
         <v>3760</v>
       </c>
-      <c r="L25" s="74">
+      <c r="L25" s="70">
         <f t="shared" si="12"/>
         <v>4260</v>
       </c>
-      <c r="M25" s="74">
+      <c r="M25" s="70">
         <f t="shared" si="12"/>
         <v>4760</v>
       </c>
-      <c r="N25" s="74">
+      <c r="N25" s="70">
         <f t="shared" si="12"/>
         <v>5260</v>
       </c>
-      <c r="O25" s="74">
+      <c r="O25" s="70">
         <f t="shared" si="12"/>
         <v>5760</v>
       </c>
-      <c r="P25" s="74">
+      <c r="P25" s="70">
         <f t="shared" si="12"/>
         <v>6260</v>
       </c>
-      <c r="Q25" s="74">
+      <c r="Q25" s="70">
         <f t="shared" si="12"/>
         <v>6760</v>
       </c>
-      <c r="R25" s="74">
+      <c r="R25" s="70">
         <f t="shared" si="12"/>
         <v>7260</v>
       </c>
-      <c r="S25" s="74">
+      <c r="S25" s="70">
         <f t="shared" si="12"/>
         <v>7760</v>
       </c>
-      <c r="T25" s="92">
+      <c r="T25" s="88">
         <f t="shared" si="12"/>
         <v>8260</v>
       </c>
-      <c r="U25" s="74">
+      <c r="U25" s="70">
         <f t="shared" si="12"/>
         <v>8760</v>
       </c>
-      <c r="V25" s="74">
+      <c r="V25" s="70">
         <f t="shared" si="12"/>
         <v>9260</v>
       </c>
-      <c r="W25" s="74">
+      <c r="W25" s="70">
         <f t="shared" si="12"/>
         <v>9760</v>
       </c>
-      <c r="X25" s="74">
+      <c r="X25" s="70">
         <f t="shared" si="12"/>
         <v>10260</v>
       </c>
-      <c r="Y25" s="74">
+      <c r="Y25" s="70">
         <f t="shared" si="12"/>
         <v>10760</v>
       </c>
-      <c r="Z25" s="74">
+      <c r="Z25" s="70">
         <f t="shared" si="12"/>
         <v>11260</v>
       </c>
-      <c r="AA25" s="74">
+      <c r="AA25" s="70">
         <f t="shared" si="12"/>
         <v>11760</v>
       </c>
-      <c r="AB25" s="74">
+      <c r="AB25" s="70">
         <f t="shared" si="12"/>
         <v>12260</v>
       </c>
-      <c r="AC25" s="73">
+      <c r="AC25" s="69">
         <f t="shared" si="12"/>
         <v>12760</v>
       </c>
-      <c r="AD25" s="73">
+      <c r="AD25" s="69">
         <f t="shared" si="12"/>
         <v>13260</v>
       </c>
@@ -4483,106 +4525,106 @@
       <c r="C26" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="E26" s="74">
+      <c r="E26" s="70">
         <v>765</v>
       </c>
-      <c r="F26" s="74">
+      <c r="F26" s="70">
         <f t="shared" si="12"/>
         <v>1265</v>
       </c>
-      <c r="G26" s="74">
+      <c r="G26" s="70">
         <f t="shared" si="12"/>
         <v>1765</v>
       </c>
-      <c r="H26" s="74">
+      <c r="H26" s="70">
         <f t="shared" si="12"/>
         <v>2265</v>
       </c>
-      <c r="I26" s="74">
+      <c r="I26" s="70">
         <f t="shared" si="12"/>
         <v>2765</v>
       </c>
-      <c r="J26" s="74">
+      <c r="J26" s="70">
         <f t="shared" si="12"/>
         <v>3265</v>
       </c>
-      <c r="K26" s="74">
+      <c r="K26" s="70">
         <f t="shared" si="12"/>
         <v>3765</v>
       </c>
-      <c r="L26" s="74">
+      <c r="L26" s="70">
         <f t="shared" si="12"/>
         <v>4265</v>
       </c>
-      <c r="M26" s="74">
+      <c r="M26" s="70">
         <f t="shared" si="12"/>
         <v>4765</v>
       </c>
-      <c r="N26" s="74">
+      <c r="N26" s="70">
         <f t="shared" si="12"/>
         <v>5265</v>
       </c>
-      <c r="O26" s="74">
+      <c r="O26" s="70">
         <f t="shared" si="12"/>
         <v>5765</v>
       </c>
-      <c r="P26" s="74">
+      <c r="P26" s="70">
         <f t="shared" si="12"/>
         <v>6265</v>
       </c>
-      <c r="Q26" s="74">
+      <c r="Q26" s="70">
         <f t="shared" si="12"/>
         <v>6765</v>
       </c>
-      <c r="R26" s="74">
+      <c r="R26" s="70">
         <f t="shared" si="12"/>
         <v>7265</v>
       </c>
-      <c r="S26" s="74">
+      <c r="S26" s="70">
         <f t="shared" si="12"/>
         <v>7765</v>
       </c>
-      <c r="T26" s="92">
+      <c r="T26" s="88">
         <f t="shared" si="12"/>
         <v>8265</v>
       </c>
-      <c r="U26" s="74">
+      <c r="U26" s="70">
         <f t="shared" si="12"/>
         <v>8765</v>
       </c>
-      <c r="V26" s="74">
+      <c r="V26" s="70">
         <f t="shared" si="12"/>
         <v>9265</v>
       </c>
-      <c r="W26" s="74">
+      <c r="W26" s="70">
         <f t="shared" si="12"/>
         <v>9765</v>
       </c>
-      <c r="X26" s="74">
+      <c r="X26" s="70">
         <f t="shared" si="12"/>
         <v>10265</v>
       </c>
-      <c r="Y26" s="74">
+      <c r="Y26" s="70">
         <f t="shared" si="12"/>
         <v>10765</v>
       </c>
-      <c r="Z26" s="74">
+      <c r="Z26" s="70">
         <f t="shared" si="12"/>
         <v>11265</v>
       </c>
-      <c r="AA26" s="74">
+      <c r="AA26" s="70">
         <f t="shared" si="12"/>
         <v>11765</v>
       </c>
-      <c r="AB26" s="74">
+      <c r="AB26" s="70">
         <f t="shared" si="12"/>
         <v>12265</v>
       </c>
-      <c r="AC26" s="73">
+      <c r="AC26" s="69">
         <f t="shared" si="12"/>
         <v>12765</v>
       </c>
-      <c r="AD26" s="73">
+      <c r="AD26" s="69">
         <f t="shared" si="12"/>
         <v>13265</v>
       </c>
@@ -4597,106 +4639,106 @@
       <c r="C27" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="E27" s="74">
+      <c r="E27" s="70">
         <v>770</v>
       </c>
-      <c r="F27" s="74">
+      <c r="F27" s="70">
         <f t="shared" si="12"/>
         <v>1270</v>
       </c>
-      <c r="G27" s="74">
+      <c r="G27" s="70">
         <f t="shared" si="12"/>
         <v>1770</v>
       </c>
-      <c r="H27" s="74">
+      <c r="H27" s="70">
         <f t="shared" si="12"/>
         <v>2270</v>
       </c>
-      <c r="I27" s="74">
+      <c r="I27" s="70">
         <f t="shared" si="12"/>
         <v>2770</v>
       </c>
-      <c r="J27" s="74">
+      <c r="J27" s="70">
         <f t="shared" si="12"/>
         <v>3270</v>
       </c>
-      <c r="K27" s="74">
+      <c r="K27" s="70">
         <f t="shared" si="12"/>
         <v>3770</v>
       </c>
-      <c r="L27" s="74">
+      <c r="L27" s="70">
         <f t="shared" si="12"/>
         <v>4270</v>
       </c>
-      <c r="M27" s="74">
+      <c r="M27" s="70">
         <f t="shared" si="12"/>
         <v>4770</v>
       </c>
-      <c r="N27" s="74">
+      <c r="N27" s="70">
         <f t="shared" si="12"/>
         <v>5270</v>
       </c>
-      <c r="O27" s="74">
+      <c r="O27" s="70">
         <f t="shared" si="12"/>
         <v>5770</v>
       </c>
-      <c r="P27" s="74">
+      <c r="P27" s="70">
         <f t="shared" si="12"/>
         <v>6270</v>
       </c>
-      <c r="Q27" s="74">
+      <c r="Q27" s="70">
         <f t="shared" si="12"/>
         <v>6770</v>
       </c>
-      <c r="R27" s="74">
+      <c r="R27" s="70">
         <f t="shared" si="12"/>
         <v>7270</v>
       </c>
-      <c r="S27" s="74">
+      <c r="S27" s="70">
         <f t="shared" si="12"/>
         <v>7770</v>
       </c>
-      <c r="T27" s="92">
+      <c r="T27" s="88">
         <f t="shared" si="12"/>
         <v>8270</v>
       </c>
-      <c r="U27" s="74">
+      <c r="U27" s="70">
         <f t="shared" si="12"/>
         <v>8770</v>
       </c>
-      <c r="V27" s="74">
+      <c r="V27" s="70">
         <f t="shared" si="12"/>
         <v>9270</v>
       </c>
-      <c r="W27" s="74">
+      <c r="W27" s="70">
         <f t="shared" si="12"/>
         <v>9770</v>
       </c>
-      <c r="X27" s="74">
+      <c r="X27" s="70">
         <f t="shared" si="12"/>
         <v>10270</v>
       </c>
-      <c r="Y27" s="74">
+      <c r="Y27" s="70">
         <f t="shared" si="12"/>
         <v>10770</v>
       </c>
-      <c r="Z27" s="74">
+      <c r="Z27" s="70">
         <f t="shared" si="12"/>
         <v>11270</v>
       </c>
-      <c r="AA27" s="74">
+      <c r="AA27" s="70">
         <f t="shared" si="12"/>
         <v>11770</v>
       </c>
-      <c r="AB27" s="74">
+      <c r="AB27" s="70">
         <f t="shared" si="12"/>
         <v>12270</v>
       </c>
-      <c r="AC27" s="73">
+      <c r="AC27" s="69">
         <f t="shared" si="12"/>
         <v>12770</v>
       </c>
-      <c r="AD27" s="73">
+      <c r="AD27" s="69">
         <f t="shared" si="12"/>
         <v>13270</v>
       </c>
@@ -4711,106 +4753,106 @@
       <c r="C28" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="E28" s="74">
+      <c r="E28" s="70">
         <v>775</v>
       </c>
-      <c r="F28" s="74">
+      <c r="F28" s="70">
         <f t="shared" si="12"/>
         <v>1275</v>
       </c>
-      <c r="G28" s="74">
+      <c r="G28" s="70">
         <f t="shared" si="12"/>
         <v>1775</v>
       </c>
-      <c r="H28" s="74">
+      <c r="H28" s="70">
         <f t="shared" si="12"/>
         <v>2275</v>
       </c>
-      <c r="I28" s="74">
+      <c r="I28" s="70">
         <f t="shared" si="12"/>
         <v>2775</v>
       </c>
-      <c r="J28" s="74">
+      <c r="J28" s="70">
         <f t="shared" si="12"/>
         <v>3275</v>
       </c>
-      <c r="K28" s="74">
+      <c r="K28" s="70">
         <f t="shared" si="12"/>
         <v>3775</v>
       </c>
-      <c r="L28" s="74">
+      <c r="L28" s="70">
         <f t="shared" si="12"/>
         <v>4275</v>
       </c>
-      <c r="M28" s="74">
+      <c r="M28" s="70">
         <f t="shared" si="12"/>
         <v>4775</v>
       </c>
-      <c r="N28" s="74">
+      <c r="N28" s="70">
         <f t="shared" si="12"/>
         <v>5275</v>
       </c>
-      <c r="O28" s="74">
+      <c r="O28" s="70">
         <f t="shared" si="12"/>
         <v>5775</v>
       </c>
-      <c r="P28" s="74">
+      <c r="P28" s="70">
         <f t="shared" si="12"/>
         <v>6275</v>
       </c>
-      <c r="Q28" s="74">
+      <c r="Q28" s="70">
         <f t="shared" si="12"/>
         <v>6775</v>
       </c>
-      <c r="R28" s="74">
+      <c r="R28" s="70">
         <f t="shared" si="12"/>
         <v>7275</v>
       </c>
-      <c r="S28" s="74">
+      <c r="S28" s="70">
         <f t="shared" si="12"/>
         <v>7775</v>
       </c>
-      <c r="T28" s="92">
+      <c r="T28" s="88">
         <f t="shared" si="12"/>
         <v>8275</v>
       </c>
-      <c r="U28" s="74">
+      <c r="U28" s="70">
         <f t="shared" si="12"/>
         <v>8775</v>
       </c>
-      <c r="V28" s="74">
+      <c r="V28" s="70">
         <f t="shared" si="12"/>
         <v>9275</v>
       </c>
-      <c r="W28" s="74">
+      <c r="W28" s="70">
         <f t="shared" si="12"/>
         <v>9775</v>
       </c>
-      <c r="X28" s="74">
+      <c r="X28" s="70">
         <f t="shared" si="12"/>
         <v>10275</v>
       </c>
-      <c r="Y28" s="74">
+      <c r="Y28" s="70">
         <f t="shared" si="12"/>
         <v>10775</v>
       </c>
-      <c r="Z28" s="74">
+      <c r="Z28" s="70">
         <f t="shared" si="12"/>
         <v>11275</v>
       </c>
-      <c r="AA28" s="74">
+      <c r="AA28" s="70">
         <f t="shared" si="12"/>
         <v>11775</v>
       </c>
-      <c r="AB28" s="74">
+      <c r="AB28" s="70">
         <f t="shared" si="12"/>
         <v>12275</v>
       </c>
-      <c r="AC28" s="73">
+      <c r="AC28" s="69">
         <f t="shared" si="12"/>
         <v>12775</v>
       </c>
-      <c r="AD28" s="73">
+      <c r="AD28" s="69">
         <f t="shared" si="12"/>
         <v>13275</v>
       </c>
@@ -4825,106 +4867,106 @@
       <c r="C29" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="E29" s="74">
+      <c r="E29" s="70">
         <v>780</v>
       </c>
-      <c r="F29" s="74">
+      <c r="F29" s="70">
         <f t="shared" si="12"/>
         <v>1280</v>
       </c>
-      <c r="G29" s="74">
+      <c r="G29" s="70">
         <f t="shared" si="12"/>
         <v>1780</v>
       </c>
-      <c r="H29" s="74">
+      <c r="H29" s="70">
         <f t="shared" si="12"/>
         <v>2280</v>
       </c>
-      <c r="I29" s="74">
+      <c r="I29" s="70">
         <f t="shared" si="12"/>
         <v>2780</v>
       </c>
-      <c r="J29" s="74">
+      <c r="J29" s="70">
         <f t="shared" si="12"/>
         <v>3280</v>
       </c>
-      <c r="K29" s="74">
+      <c r="K29" s="70">
         <f t="shared" si="12"/>
         <v>3780</v>
       </c>
-      <c r="L29" s="74">
+      <c r="L29" s="70">
         <f t="shared" si="12"/>
         <v>4280</v>
       </c>
-      <c r="M29" s="74">
+      <c r="M29" s="70">
         <f t="shared" si="12"/>
         <v>4780</v>
       </c>
-      <c r="N29" s="74">
+      <c r="N29" s="70">
         <f t="shared" si="12"/>
         <v>5280</v>
       </c>
-      <c r="O29" s="74">
+      <c r="O29" s="70">
         <f t="shared" si="12"/>
         <v>5780</v>
       </c>
-      <c r="P29" s="74">
+      <c r="P29" s="70">
         <f t="shared" si="12"/>
         <v>6280</v>
       </c>
-      <c r="Q29" s="74">
+      <c r="Q29" s="70">
         <f t="shared" si="12"/>
         <v>6780</v>
       </c>
-      <c r="R29" s="74">
+      <c r="R29" s="70">
         <f t="shared" si="12"/>
         <v>7280</v>
       </c>
-      <c r="S29" s="74">
+      <c r="S29" s="70">
         <f t="shared" si="12"/>
         <v>7780</v>
       </c>
-      <c r="T29" s="92">
+      <c r="T29" s="88">
         <f t="shared" si="12"/>
         <v>8280</v>
       </c>
-      <c r="U29" s="74">
+      <c r="U29" s="70">
         <f t="shared" si="12"/>
         <v>8780</v>
       </c>
-      <c r="V29" s="74">
+      <c r="V29" s="70">
         <f t="shared" si="12"/>
         <v>9280</v>
       </c>
-      <c r="W29" s="74">
+      <c r="W29" s="70">
         <f t="shared" si="12"/>
         <v>9780</v>
       </c>
-      <c r="X29" s="74">
+      <c r="X29" s="70">
         <f t="shared" si="12"/>
         <v>10280</v>
       </c>
-      <c r="Y29" s="74">
+      <c r="Y29" s="70">
         <f t="shared" si="12"/>
         <v>10780</v>
       </c>
-      <c r="Z29" s="74">
+      <c r="Z29" s="70">
         <f t="shared" si="12"/>
         <v>11280</v>
       </c>
-      <c r="AA29" s="74">
+      <c r="AA29" s="70">
         <f t="shared" si="12"/>
         <v>11780</v>
       </c>
-      <c r="AB29" s="74">
+      <c r="AB29" s="70">
         <f t="shared" si="12"/>
         <v>12280</v>
       </c>
-      <c r="AC29" s="73">
+      <c r="AC29" s="69">
         <f t="shared" si="12"/>
         <v>12780</v>
       </c>
-      <c r="AD29" s="73">
+      <c r="AD29" s="69">
         <f t="shared" si="12"/>
         <v>13280</v>
       </c>
@@ -4939,106 +4981,106 @@
       <c r="C30" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="E30" s="74">
+      <c r="E30" s="70">
         <v>785</v>
       </c>
-      <c r="F30" s="74">
+      <c r="F30" s="70">
         <f t="shared" si="12"/>
         <v>1285</v>
       </c>
-      <c r="G30" s="74">
+      <c r="G30" s="70">
         <f t="shared" si="12"/>
         <v>1785</v>
       </c>
-      <c r="H30" s="74">
+      <c r="H30" s="70">
         <f t="shared" si="12"/>
         <v>2285</v>
       </c>
-      <c r="I30" s="74">
+      <c r="I30" s="70">
         <f t="shared" si="12"/>
         <v>2785</v>
       </c>
-      <c r="J30" s="74">
+      <c r="J30" s="70">
         <f t="shared" si="12"/>
         <v>3285</v>
       </c>
-      <c r="K30" s="74">
+      <c r="K30" s="70">
         <f t="shared" ref="K30:AD30" si="13">SUM(J30, 500)</f>
         <v>3785</v>
       </c>
-      <c r="L30" s="74">
+      <c r="L30" s="70">
         <f t="shared" si="13"/>
         <v>4285</v>
       </c>
-      <c r="M30" s="74">
+      <c r="M30" s="70">
         <f t="shared" si="13"/>
         <v>4785</v>
       </c>
-      <c r="N30" s="74">
+      <c r="N30" s="70">
         <f t="shared" si="13"/>
         <v>5285</v>
       </c>
-      <c r="O30" s="74">
+      <c r="O30" s="70">
         <f t="shared" si="13"/>
         <v>5785</v>
       </c>
-      <c r="P30" s="74">
+      <c r="P30" s="70">
         <f t="shared" si="13"/>
         <v>6285</v>
       </c>
-      <c r="Q30" s="74">
+      <c r="Q30" s="70">
         <f t="shared" si="13"/>
         <v>6785</v>
       </c>
-      <c r="R30" s="74">
+      <c r="R30" s="70">
         <f t="shared" si="13"/>
         <v>7285</v>
       </c>
-      <c r="S30" s="74">
+      <c r="S30" s="70">
         <f t="shared" si="13"/>
         <v>7785</v>
       </c>
-      <c r="T30" s="92">
+      <c r="T30" s="88">
         <f t="shared" si="13"/>
         <v>8285</v>
       </c>
-      <c r="U30" s="74">
+      <c r="U30" s="70">
         <f t="shared" si="13"/>
         <v>8785</v>
       </c>
-      <c r="V30" s="74">
+      <c r="V30" s="70">
         <f t="shared" si="13"/>
         <v>9285</v>
       </c>
-      <c r="W30" s="74">
+      <c r="W30" s="70">
         <f t="shared" si="13"/>
         <v>9785</v>
       </c>
-      <c r="X30" s="74">
+      <c r="X30" s="70">
         <f t="shared" si="13"/>
         <v>10285</v>
       </c>
-      <c r="Y30" s="74">
+      <c r="Y30" s="70">
         <f t="shared" si="13"/>
         <v>10785</v>
       </c>
-      <c r="Z30" s="74">
+      <c r="Z30" s="70">
         <f t="shared" si="13"/>
         <v>11285</v>
       </c>
-      <c r="AA30" s="74">
+      <c r="AA30" s="70">
         <f t="shared" si="13"/>
         <v>11785</v>
       </c>
-      <c r="AB30" s="74">
+      <c r="AB30" s="70">
         <f t="shared" si="13"/>
         <v>12285</v>
       </c>
-      <c r="AC30" s="73">
+      <c r="AC30" s="69">
         <f t="shared" si="13"/>
         <v>12785</v>
       </c>
-      <c r="AD30" s="73">
+      <c r="AD30" s="69">
         <f t="shared" si="13"/>
         <v>13285</v>
       </c>
@@ -5056,106 +5098,106 @@
       <c r="D31" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="E31" s="91">
+      <c r="E31" s="87">
         <v>5</v>
       </c>
-      <c r="F31" s="91">
+      <c r="F31" s="87">
         <f>SUM(E31,3)</f>
         <v>8</v>
       </c>
-      <c r="G31" s="91">
+      <c r="G31" s="87">
         <f t="shared" ref="G31:AD37" si="14">SUM(F31,3)</f>
         <v>11</v>
       </c>
-      <c r="H31" s="91">
+      <c r="H31" s="87">
         <f t="shared" si="14"/>
         <v>14</v>
       </c>
-      <c r="I31" s="91">
+      <c r="I31" s="87">
         <f t="shared" si="14"/>
         <v>17</v>
       </c>
-      <c r="J31" s="91">
+      <c r="J31" s="87">
         <f t="shared" si="14"/>
         <v>20</v>
       </c>
-      <c r="K31" s="91">
+      <c r="K31" s="87">
         <f t="shared" si="14"/>
         <v>23</v>
       </c>
-      <c r="L31" s="91">
+      <c r="L31" s="87">
         <f t="shared" si="14"/>
         <v>26</v>
       </c>
-      <c r="M31" s="91">
+      <c r="M31" s="87">
         <f t="shared" si="14"/>
         <v>29</v>
       </c>
-      <c r="N31" s="91">
+      <c r="N31" s="87">
         <f t="shared" si="14"/>
         <v>32</v>
       </c>
-      <c r="O31" s="91">
+      <c r="O31" s="87">
         <f t="shared" si="14"/>
         <v>35</v>
       </c>
-      <c r="P31" s="91">
+      <c r="P31" s="87">
         <f t="shared" si="14"/>
         <v>38</v>
       </c>
-      <c r="Q31" s="91">
+      <c r="Q31" s="87">
         <f t="shared" si="14"/>
         <v>41</v>
       </c>
-      <c r="R31" s="91">
+      <c r="R31" s="87">
         <f t="shared" si="14"/>
         <v>44</v>
       </c>
-      <c r="S31" s="91">
+      <c r="S31" s="87">
         <f t="shared" si="14"/>
         <v>47</v>
       </c>
-      <c r="T31" s="93">
+      <c r="T31" s="89">
         <f t="shared" si="14"/>
         <v>50</v>
       </c>
-      <c r="U31" s="91">
+      <c r="U31" s="87">
         <f t="shared" si="14"/>
         <v>53</v>
       </c>
-      <c r="V31" s="91">
+      <c r="V31" s="87">
         <f t="shared" si="14"/>
         <v>56</v>
       </c>
-      <c r="W31" s="91">
+      <c r="W31" s="87">
         <f t="shared" si="14"/>
         <v>59</v>
       </c>
-      <c r="X31" s="91">
+      <c r="X31" s="87">
         <f t="shared" si="14"/>
         <v>62</v>
       </c>
-      <c r="Y31" s="91">
+      <c r="Y31" s="87">
         <f t="shared" si="14"/>
         <v>65</v>
       </c>
-      <c r="Z31" s="91">
+      <c r="Z31" s="87">
         <f t="shared" si="14"/>
         <v>68</v>
       </c>
-      <c r="AA31" s="91">
+      <c r="AA31" s="87">
         <f t="shared" si="14"/>
         <v>71</v>
       </c>
-      <c r="AB31" s="91">
+      <c r="AB31" s="87">
         <f t="shared" si="14"/>
         <v>74</v>
       </c>
-      <c r="AC31" s="91">
+      <c r="AC31" s="87">
         <f t="shared" si="14"/>
         <v>77</v>
       </c>
-      <c r="AD31" s="91">
+      <c r="AD31" s="87">
         <f t="shared" si="14"/>
         <v>80</v>
       </c>
@@ -5173,106 +5215,106 @@
       <c r="D32" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E32" s="90">
+      <c r="E32" s="86">
         <v>5.01</v>
       </c>
-      <c r="F32" s="90">
+      <c r="F32" s="86">
         <f t="shared" ref="F32:U37" si="15">SUM(E32,3)</f>
         <v>8.01</v>
       </c>
-      <c r="G32" s="90">
+      <c r="G32" s="86">
         <f t="shared" si="15"/>
         <v>11.01</v>
       </c>
-      <c r="H32" s="90">
+      <c r="H32" s="86">
         <f t="shared" si="15"/>
         <v>14.01</v>
       </c>
-      <c r="I32" s="90">
+      <c r="I32" s="86">
         <f t="shared" si="15"/>
         <v>17.009999999999998</v>
       </c>
-      <c r="J32" s="90">
+      <c r="J32" s="86">
         <f t="shared" si="15"/>
         <v>20.009999999999998</v>
       </c>
-      <c r="K32" s="90">
+      <c r="K32" s="86">
         <f t="shared" si="15"/>
         <v>23.009999999999998</v>
       </c>
-      <c r="L32" s="90">
+      <c r="L32" s="86">
         <f t="shared" si="15"/>
         <v>26.009999999999998</v>
       </c>
-      <c r="M32" s="90">
+      <c r="M32" s="86">
         <f t="shared" si="15"/>
         <v>29.009999999999998</v>
       </c>
-      <c r="N32" s="90">
+      <c r="N32" s="86">
         <f t="shared" si="15"/>
         <v>32.01</v>
       </c>
-      <c r="O32" s="90">
+      <c r="O32" s="86">
         <f t="shared" si="15"/>
         <v>35.01</v>
       </c>
-      <c r="P32" s="90">
+      <c r="P32" s="86">
         <f t="shared" si="15"/>
         <v>38.01</v>
       </c>
-      <c r="Q32" s="90">
+      <c r="Q32" s="86">
         <f t="shared" si="15"/>
         <v>41.01</v>
       </c>
-      <c r="R32" s="90">
+      <c r="R32" s="86">
         <f t="shared" si="15"/>
         <v>44.01</v>
       </c>
-      <c r="S32" s="90">
+      <c r="S32" s="86">
         <f t="shared" si="15"/>
         <v>47.01</v>
       </c>
-      <c r="T32" s="94">
+      <c r="T32" s="90">
         <f t="shared" si="15"/>
         <v>50.01</v>
       </c>
-      <c r="U32" s="90">
+      <c r="U32" s="86">
         <f t="shared" si="15"/>
         <v>53.01</v>
       </c>
-      <c r="V32" s="90">
+      <c r="V32" s="86">
         <f t="shared" si="14"/>
         <v>56.01</v>
       </c>
-      <c r="W32" s="90">
+      <c r="W32" s="86">
         <f t="shared" si="14"/>
         <v>59.01</v>
       </c>
-      <c r="X32" s="90">
+      <c r="X32" s="86">
         <f t="shared" si="14"/>
         <v>62.01</v>
       </c>
-      <c r="Y32" s="90">
+      <c r="Y32" s="86">
         <f t="shared" si="14"/>
         <v>65.009999999999991</v>
       </c>
-      <c r="Z32" s="90">
+      <c r="Z32" s="86">
         <f t="shared" si="14"/>
         <v>68.009999999999991</v>
       </c>
-      <c r="AA32" s="90">
+      <c r="AA32" s="86">
         <f t="shared" si="14"/>
         <v>71.009999999999991</v>
       </c>
-      <c r="AB32" s="90">
+      <c r="AB32" s="86">
         <f t="shared" si="14"/>
         <v>74.009999999999991</v>
       </c>
-      <c r="AC32" s="90">
+      <c r="AC32" s="86">
         <f t="shared" si="14"/>
         <v>77.009999999999991</v>
       </c>
-      <c r="AD32" s="90">
+      <c r="AD32" s="86">
         <f t="shared" si="14"/>
         <v>80.009999999999991</v>
       </c>
@@ -5290,106 +5332,106 @@
       <c r="D33" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E33" s="90">
+      <c r="E33" s="86">
         <v>5.0199999999999996</v>
       </c>
-      <c r="F33" s="90">
+      <c r="F33" s="86">
         <f t="shared" si="15"/>
         <v>8.02</v>
       </c>
-      <c r="G33" s="90">
+      <c r="G33" s="86">
         <f t="shared" si="14"/>
         <v>11.02</v>
       </c>
-      <c r="H33" s="90">
+      <c r="H33" s="86">
         <f t="shared" si="14"/>
         <v>14.02</v>
       </c>
-      <c r="I33" s="90">
+      <c r="I33" s="86">
         <f t="shared" si="14"/>
         <v>17.02</v>
       </c>
-      <c r="J33" s="90">
+      <c r="J33" s="86">
         <f t="shared" si="14"/>
         <v>20.02</v>
       </c>
-      <c r="K33" s="90">
+      <c r="K33" s="86">
         <f t="shared" si="14"/>
         <v>23.02</v>
       </c>
-      <c r="L33" s="90">
+      <c r="L33" s="86">
         <f t="shared" si="14"/>
         <v>26.02</v>
       </c>
-      <c r="M33" s="90">
+      <c r="M33" s="86">
         <f t="shared" si="14"/>
         <v>29.02</v>
       </c>
-      <c r="N33" s="90">
+      <c r="N33" s="86">
         <f t="shared" si="14"/>
         <v>32.019999999999996</v>
       </c>
-      <c r="O33" s="90">
+      <c r="O33" s="86">
         <f t="shared" si="14"/>
         <v>35.019999999999996</v>
       </c>
-      <c r="P33" s="90">
+      <c r="P33" s="86">
         <f t="shared" si="14"/>
         <v>38.019999999999996</v>
       </c>
-      <c r="Q33" s="90">
+      <c r="Q33" s="86">
         <f t="shared" si="14"/>
         <v>41.019999999999996</v>
       </c>
-      <c r="R33" s="90">
+      <c r="R33" s="86">
         <f t="shared" si="14"/>
         <v>44.019999999999996</v>
       </c>
-      <c r="S33" s="90">
+      <c r="S33" s="86">
         <f t="shared" si="14"/>
         <v>47.019999999999996</v>
       </c>
-      <c r="T33" s="94">
+      <c r="T33" s="90">
         <f t="shared" si="14"/>
         <v>50.019999999999996</v>
       </c>
-      <c r="U33" s="90">
+      <c r="U33" s="86">
         <f t="shared" si="14"/>
         <v>53.019999999999996</v>
       </c>
-      <c r="V33" s="90">
+      <c r="V33" s="86">
         <f t="shared" si="14"/>
         <v>56.019999999999996</v>
       </c>
-      <c r="W33" s="90">
+      <c r="W33" s="86">
         <f t="shared" si="14"/>
         <v>59.019999999999996</v>
       </c>
-      <c r="X33" s="90">
+      <c r="X33" s="86">
         <f t="shared" si="14"/>
         <v>62.019999999999996</v>
       </c>
-      <c r="Y33" s="90">
+      <c r="Y33" s="86">
         <f t="shared" si="14"/>
         <v>65.02</v>
       </c>
-      <c r="Z33" s="90">
+      <c r="Z33" s="86">
         <f t="shared" si="14"/>
         <v>68.02</v>
       </c>
-      <c r="AA33" s="90">
+      <c r="AA33" s="86">
         <f t="shared" si="14"/>
         <v>71.02</v>
       </c>
-      <c r="AB33" s="90">
+      <c r="AB33" s="86">
         <f t="shared" si="14"/>
         <v>74.02</v>
       </c>
-      <c r="AC33" s="90">
+      <c r="AC33" s="86">
         <f t="shared" si="14"/>
         <v>77.02</v>
       </c>
-      <c r="AD33" s="90">
+      <c r="AD33" s="86">
         <f t="shared" si="14"/>
         <v>80.02</v>
       </c>
@@ -5407,223 +5449,223 @@
       <c r="D34" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E34" s="90">
+      <c r="E34" s="86">
         <v>5.03</v>
       </c>
-      <c r="F34" s="90">
+      <c r="F34" s="86">
         <f t="shared" si="15"/>
         <v>8.0300000000000011</v>
       </c>
-      <c r="G34" s="90">
+      <c r="G34" s="86">
         <f t="shared" si="14"/>
         <v>11.030000000000001</v>
       </c>
-      <c r="H34" s="90">
+      <c r="H34" s="86">
         <f t="shared" si="14"/>
         <v>14.030000000000001</v>
       </c>
-      <c r="I34" s="90">
+      <c r="I34" s="86">
         <f t="shared" si="14"/>
         <v>17.03</v>
       </c>
-      <c r="J34" s="90">
+      <c r="J34" s="86">
         <f t="shared" si="14"/>
         <v>20.03</v>
       </c>
-      <c r="K34" s="90">
+      <c r="K34" s="86">
         <f t="shared" si="14"/>
         <v>23.03</v>
       </c>
-      <c r="L34" s="90">
+      <c r="L34" s="86">
         <f t="shared" si="14"/>
         <v>26.03</v>
       </c>
-      <c r="M34" s="90">
+      <c r="M34" s="86">
         <f t="shared" si="14"/>
         <v>29.03</v>
       </c>
-      <c r="N34" s="90">
+      <c r="N34" s="86">
         <f t="shared" si="14"/>
         <v>32.03</v>
       </c>
-      <c r="O34" s="90">
+      <c r="O34" s="86">
         <f t="shared" si="14"/>
         <v>35.03</v>
       </c>
-      <c r="P34" s="90">
+      <c r="P34" s="86">
         <f t="shared" si="14"/>
         <v>38.03</v>
       </c>
-      <c r="Q34" s="90">
+      <c r="Q34" s="86">
         <f t="shared" si="14"/>
         <v>41.03</v>
       </c>
-      <c r="R34" s="90">
+      <c r="R34" s="86">
         <f t="shared" si="14"/>
         <v>44.03</v>
       </c>
-      <c r="S34" s="90">
+      <c r="S34" s="86">
         <f t="shared" si="14"/>
         <v>47.03</v>
       </c>
-      <c r="T34" s="94">
+      <c r="T34" s="90">
         <f t="shared" si="14"/>
         <v>50.03</v>
       </c>
-      <c r="U34" s="90">
+      <c r="U34" s="86">
         <f t="shared" si="14"/>
         <v>53.03</v>
       </c>
-      <c r="V34" s="90">
+      <c r="V34" s="86">
         <f t="shared" si="14"/>
         <v>56.03</v>
       </c>
-      <c r="W34" s="90">
+      <c r="W34" s="86">
         <f t="shared" si="14"/>
         <v>59.03</v>
       </c>
-      <c r="X34" s="90">
+      <c r="X34" s="86">
         <f t="shared" si="14"/>
         <v>62.03</v>
       </c>
-      <c r="Y34" s="90">
+      <c r="Y34" s="86">
         <f t="shared" si="14"/>
         <v>65.03</v>
       </c>
-      <c r="Z34" s="90">
+      <c r="Z34" s="86">
         <f t="shared" si="14"/>
         <v>68.03</v>
       </c>
-      <c r="AA34" s="90">
+      <c r="AA34" s="86">
         <f t="shared" si="14"/>
         <v>71.03</v>
       </c>
-      <c r="AB34" s="90">
+      <c r="AB34" s="86">
         <f t="shared" si="14"/>
         <v>74.03</v>
       </c>
-      <c r="AC34" s="90">
+      <c r="AC34" s="86">
         <f t="shared" si="14"/>
         <v>77.03</v>
       </c>
-      <c r="AD34" s="90">
+      <c r="AD34" s="86">
         <f t="shared" si="14"/>
         <v>80.03</v>
       </c>
     </row>
     <row r="35" spans="1:30" x14ac:dyDescent="0.35">
-      <c r="A35" s="68" t="s">
+      <c r="A35" s="64" t="s">
         <v>118</v>
       </c>
-      <c r="B35" s="69" t="s">
+      <c r="B35" s="65" t="s">
         <v>16</v>
       </c>
-      <c r="C35" s="70" t="s">
+      <c r="C35" s="66" t="s">
         <v>19</v>
       </c>
-      <c r="D35" s="70" t="s">
+      <c r="D35" s="66" t="s">
         <v>47</v>
       </c>
-      <c r="E35" s="58">
+      <c r="E35" s="57">
         <v>7</v>
       </c>
-      <c r="F35" s="58">
+      <c r="F35" s="57">
         <f t="shared" si="15"/>
         <v>10</v>
       </c>
-      <c r="G35" s="58">
+      <c r="G35" s="57">
         <f t="shared" si="14"/>
         <v>13</v>
       </c>
-      <c r="H35" s="58">
+      <c r="H35" s="57">
         <f t="shared" si="14"/>
         <v>16</v>
       </c>
-      <c r="I35" s="58">
+      <c r="I35" s="57">
         <f t="shared" si="14"/>
         <v>19</v>
       </c>
-      <c r="J35" s="58">
+      <c r="J35" s="57">
         <f t="shared" si="14"/>
         <v>22</v>
       </c>
-      <c r="K35" s="58">
+      <c r="K35" s="57">
         <f t="shared" si="14"/>
         <v>25</v>
       </c>
-      <c r="L35" s="58">
+      <c r="L35" s="57">
         <f t="shared" si="14"/>
         <v>28</v>
       </c>
-      <c r="M35" s="58">
+      <c r="M35" s="57">
         <f t="shared" si="14"/>
         <v>31</v>
       </c>
-      <c r="N35" s="58">
+      <c r="N35" s="57">
         <f t="shared" si="14"/>
         <v>34</v>
       </c>
-      <c r="O35" s="58">
+      <c r="O35" s="57">
         <f t="shared" si="14"/>
         <v>37</v>
       </c>
-      <c r="P35" s="58">
+      <c r="P35" s="57">
         <f t="shared" si="14"/>
         <v>40</v>
       </c>
-      <c r="Q35" s="58">
+      <c r="Q35" s="57">
         <f t="shared" si="14"/>
         <v>43</v>
       </c>
-      <c r="R35" s="58">
+      <c r="R35" s="57">
         <f t="shared" si="14"/>
         <v>46</v>
       </c>
-      <c r="S35" s="58">
+      <c r="S35" s="57">
         <f t="shared" si="14"/>
         <v>49</v>
       </c>
-      <c r="T35" s="58">
+      <c r="T35" s="57">
         <f t="shared" si="14"/>
         <v>52</v>
       </c>
-      <c r="U35" s="58">
+      <c r="U35" s="57">
         <f t="shared" si="14"/>
         <v>55</v>
       </c>
-      <c r="V35" s="58">
+      <c r="V35" s="57">
         <f t="shared" si="14"/>
         <v>58</v>
       </c>
-      <c r="W35" s="58">
+      <c r="W35" s="57">
         <f t="shared" si="14"/>
         <v>61</v>
       </c>
-      <c r="X35" s="58">
+      <c r="X35" s="57">
         <f t="shared" si="14"/>
         <v>64</v>
       </c>
-      <c r="Y35" s="58">
+      <c r="Y35" s="57">
         <f t="shared" si="14"/>
         <v>67</v>
       </c>
-      <c r="Z35" s="58">
+      <c r="Z35" s="57">
         <f t="shared" si="14"/>
         <v>70</v>
       </c>
-      <c r="AA35" s="58">
+      <c r="AA35" s="57">
         <f t="shared" si="14"/>
         <v>73</v>
       </c>
-      <c r="AB35" s="58">
+      <c r="AB35" s="57">
         <f t="shared" si="14"/>
         <v>76</v>
       </c>
-      <c r="AC35" s="58">
+      <c r="AC35" s="57">
         <f t="shared" si="14"/>
         <v>79</v>
       </c>
-      <c r="AD35" s="58">
+      <c r="AD35" s="57">
         <f t="shared" si="14"/>
         <v>82</v>
       </c>
@@ -5641,106 +5683,106 @@
       <c r="D36" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E36" s="90">
+      <c r="E36" s="86">
         <v>5.05</v>
       </c>
-      <c r="F36" s="90">
+      <c r="F36" s="86">
         <f t="shared" si="15"/>
         <v>8.0500000000000007</v>
       </c>
-      <c r="G36" s="90">
+      <c r="G36" s="86">
         <f t="shared" si="14"/>
         <v>11.05</v>
       </c>
-      <c r="H36" s="90">
+      <c r="H36" s="86">
         <f t="shared" si="14"/>
         <v>14.05</v>
       </c>
-      <c r="I36" s="90">
+      <c r="I36" s="86">
         <f t="shared" si="14"/>
         <v>17.05</v>
       </c>
-      <c r="J36" s="90">
+      <c r="J36" s="86">
         <f t="shared" si="14"/>
         <v>20.05</v>
       </c>
-      <c r="K36" s="90">
+      <c r="K36" s="86">
         <f t="shared" si="14"/>
         <v>23.05</v>
       </c>
-      <c r="L36" s="90">
+      <c r="L36" s="86">
         <f t="shared" si="14"/>
         <v>26.05</v>
       </c>
-      <c r="M36" s="90">
+      <c r="M36" s="86">
         <f t="shared" si="14"/>
         <v>29.05</v>
       </c>
-      <c r="N36" s="90">
+      <c r="N36" s="86">
         <f t="shared" si="14"/>
         <v>32.049999999999997</v>
       </c>
-      <c r="O36" s="90">
+      <c r="O36" s="86">
         <f t="shared" si="14"/>
         <v>35.049999999999997</v>
       </c>
-      <c r="P36" s="90">
+      <c r="P36" s="86">
         <f t="shared" si="14"/>
         <v>38.049999999999997</v>
       </c>
-      <c r="Q36" s="90">
+      <c r="Q36" s="86">
         <f t="shared" si="14"/>
         <v>41.05</v>
       </c>
-      <c r="R36" s="90">
+      <c r="R36" s="86">
         <f t="shared" si="14"/>
         <v>44.05</v>
       </c>
-      <c r="S36" s="90">
+      <c r="S36" s="86">
         <f t="shared" si="14"/>
         <v>47.05</v>
       </c>
-      <c r="T36" s="94">
+      <c r="T36" s="90">
         <f t="shared" si="14"/>
         <v>50.05</v>
       </c>
-      <c r="U36" s="90">
+      <c r="U36" s="86">
         <f t="shared" si="14"/>
         <v>53.05</v>
       </c>
-      <c r="V36" s="90">
+      <c r="V36" s="86">
         <f t="shared" si="14"/>
         <v>56.05</v>
       </c>
-      <c r="W36" s="90">
+      <c r="W36" s="86">
         <f t="shared" si="14"/>
         <v>59.05</v>
       </c>
-      <c r="X36" s="90">
+      <c r="X36" s="86">
         <f t="shared" si="14"/>
         <v>62.05</v>
       </c>
-      <c r="Y36" s="90">
+      <c r="Y36" s="86">
         <f t="shared" si="14"/>
         <v>65.05</v>
       </c>
-      <c r="Z36" s="90">
+      <c r="Z36" s="86">
         <f t="shared" si="14"/>
         <v>68.05</v>
       </c>
-      <c r="AA36" s="90">
+      <c r="AA36" s="86">
         <f t="shared" si="14"/>
         <v>71.05</v>
       </c>
-      <c r="AB36" s="90">
+      <c r="AB36" s="86">
         <f t="shared" si="14"/>
         <v>74.05</v>
       </c>
-      <c r="AC36" s="90">
+      <c r="AC36" s="86">
         <f t="shared" si="14"/>
         <v>77.05</v>
       </c>
-      <c r="AD36" s="90">
+      <c r="AD36" s="86">
         <f t="shared" si="14"/>
         <v>80.05</v>
       </c>
@@ -5758,106 +5800,106 @@
       <c r="D37" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E37" s="90">
+      <c r="E37" s="86">
         <v>5.0599999999999996</v>
       </c>
-      <c r="F37" s="90">
+      <c r="F37" s="86">
         <f t="shared" si="15"/>
         <v>8.0599999999999987</v>
       </c>
-      <c r="G37" s="90">
+      <c r="G37" s="86">
         <f t="shared" si="14"/>
         <v>11.059999999999999</v>
       </c>
-      <c r="H37" s="90">
+      <c r="H37" s="86">
         <f t="shared" si="14"/>
         <v>14.059999999999999</v>
       </c>
-      <c r="I37" s="90">
+      <c r="I37" s="86">
         <f t="shared" si="14"/>
         <v>17.059999999999999</v>
       </c>
-      <c r="J37" s="90">
+      <c r="J37" s="86">
         <f t="shared" si="14"/>
         <v>20.059999999999999</v>
       </c>
-      <c r="K37" s="90">
+      <c r="K37" s="86">
         <f t="shared" si="14"/>
         <v>23.06</v>
       </c>
-      <c r="L37" s="90">
+      <c r="L37" s="86">
         <f t="shared" si="14"/>
         <v>26.06</v>
       </c>
-      <c r="M37" s="90">
+      <c r="M37" s="86">
         <f t="shared" si="14"/>
         <v>29.06</v>
       </c>
-      <c r="N37" s="90">
+      <c r="N37" s="86">
         <f t="shared" si="14"/>
         <v>32.06</v>
       </c>
-      <c r="O37" s="90">
+      <c r="O37" s="86">
         <f t="shared" si="14"/>
         <v>35.06</v>
       </c>
-      <c r="P37" s="90">
+      <c r="P37" s="86">
         <f t="shared" si="14"/>
         <v>38.06</v>
       </c>
-      <c r="Q37" s="90">
+      <c r="Q37" s="86">
         <f t="shared" si="14"/>
         <v>41.06</v>
       </c>
-      <c r="R37" s="90">
+      <c r="R37" s="86">
         <f t="shared" si="14"/>
         <v>44.06</v>
       </c>
-      <c r="S37" s="90">
+      <c r="S37" s="86">
         <f t="shared" si="14"/>
         <v>47.06</v>
       </c>
-      <c r="T37" s="94">
+      <c r="T37" s="90">
         <f t="shared" si="14"/>
         <v>50.06</v>
       </c>
-      <c r="U37" s="90">
+      <c r="U37" s="86">
         <f t="shared" si="14"/>
         <v>53.06</v>
       </c>
-      <c r="V37" s="90">
+      <c r="V37" s="86">
         <f t="shared" si="14"/>
         <v>56.06</v>
       </c>
-      <c r="W37" s="90">
+      <c r="W37" s="86">
         <f t="shared" si="14"/>
         <v>59.06</v>
       </c>
-      <c r="X37" s="90">
+      <c r="X37" s="86">
         <f t="shared" si="14"/>
         <v>62.06</v>
       </c>
-      <c r="Y37" s="90">
+      <c r="Y37" s="86">
         <f t="shared" si="14"/>
         <v>65.06</v>
       </c>
-      <c r="Z37" s="90">
+      <c r="Z37" s="86">
         <f t="shared" si="14"/>
         <v>68.06</v>
       </c>
-      <c r="AA37" s="90">
+      <c r="AA37" s="86">
         <f t="shared" si="14"/>
         <v>71.06</v>
       </c>
-      <c r="AB37" s="90">
+      <c r="AB37" s="86">
         <f t="shared" si="14"/>
         <v>74.06</v>
       </c>
-      <c r="AC37" s="90">
+      <c r="AC37" s="86">
         <f t="shared" si="14"/>
         <v>77.06</v>
       </c>
-      <c r="AD37" s="90">
+      <c r="AD37" s="86">
         <f t="shared" si="14"/>
         <v>80.06</v>
       </c>
@@ -5875,106 +5917,106 @@
       <c r="D38" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E38" s="90">
+      <c r="E38" s="86">
         <v>6</v>
       </c>
-      <c r="F38" s="90">
+      <c r="F38" s="86">
         <f>SUM(E38,3)</f>
         <v>9</v>
       </c>
-      <c r="G38" s="90">
+      <c r="G38" s="86">
         <f t="shared" ref="G38:AD43" si="16">SUM(F38,3)</f>
         <v>12</v>
       </c>
-      <c r="H38" s="90">
+      <c r="H38" s="86">
         <f t="shared" si="16"/>
         <v>15</v>
       </c>
-      <c r="I38" s="90">
+      <c r="I38" s="86">
         <f t="shared" si="16"/>
         <v>18</v>
       </c>
-      <c r="J38" s="90">
+      <c r="J38" s="86">
         <f t="shared" si="16"/>
         <v>21</v>
       </c>
-      <c r="K38" s="90">
+      <c r="K38" s="86">
         <f t="shared" si="16"/>
         <v>24</v>
       </c>
-      <c r="L38" s="90">
+      <c r="L38" s="86">
         <f t="shared" si="16"/>
         <v>27</v>
       </c>
-      <c r="M38" s="90">
+      <c r="M38" s="86">
         <f t="shared" si="16"/>
         <v>30</v>
       </c>
-      <c r="N38" s="90">
+      <c r="N38" s="86">
         <f t="shared" si="16"/>
         <v>33</v>
       </c>
-      <c r="O38" s="90">
+      <c r="O38" s="86">
         <f t="shared" si="16"/>
         <v>36</v>
       </c>
-      <c r="P38" s="90">
+      <c r="P38" s="86">
         <f t="shared" si="16"/>
         <v>39</v>
       </c>
-      <c r="Q38" s="90">
+      <c r="Q38" s="86">
         <f t="shared" si="16"/>
         <v>42</v>
       </c>
-      <c r="R38" s="90">
+      <c r="R38" s="86">
         <f t="shared" si="16"/>
         <v>45</v>
       </c>
-      <c r="S38" s="90">
+      <c r="S38" s="86">
         <f t="shared" si="16"/>
         <v>48</v>
       </c>
-      <c r="T38" s="94">
+      <c r="T38" s="90">
         <f t="shared" si="16"/>
         <v>51</v>
       </c>
-      <c r="U38" s="90">
+      <c r="U38" s="86">
         <f t="shared" si="16"/>
         <v>54</v>
       </c>
-      <c r="V38" s="90">
+      <c r="V38" s="86">
         <f t="shared" si="16"/>
         <v>57</v>
       </c>
-      <c r="W38" s="90">
+      <c r="W38" s="86">
         <f t="shared" si="16"/>
         <v>60</v>
       </c>
-      <c r="X38" s="90">
+      <c r="X38" s="86">
         <f t="shared" si="16"/>
         <v>63</v>
       </c>
-      <c r="Y38" s="90">
+      <c r="Y38" s="86">
         <f t="shared" si="16"/>
         <v>66</v>
       </c>
-      <c r="Z38" s="90">
+      <c r="Z38" s="86">
         <f t="shared" si="16"/>
         <v>69</v>
       </c>
-      <c r="AA38" s="90">
+      <c r="AA38" s="86">
         <f t="shared" si="16"/>
         <v>72</v>
       </c>
-      <c r="AB38" s="90">
+      <c r="AB38" s="86">
         <f t="shared" si="16"/>
         <v>75</v>
       </c>
-      <c r="AC38" s="90">
+      <c r="AC38" s="86">
         <f t="shared" si="16"/>
         <v>78</v>
       </c>
-      <c r="AD38" s="90">
+      <c r="AD38" s="86">
         <f t="shared" si="16"/>
         <v>81</v>
       </c>
@@ -5992,106 +6034,106 @@
       <c r="D39" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E39" s="90">
+      <c r="E39" s="86">
         <v>6.01</v>
       </c>
-      <c r="F39" s="90">
+      <c r="F39" s="86">
         <f t="shared" ref="F39:U43" si="17">SUM(E39,3)</f>
         <v>9.01</v>
       </c>
-      <c r="G39" s="90">
+      <c r="G39" s="86">
         <f t="shared" si="17"/>
         <v>12.01</v>
       </c>
-      <c r="H39" s="90">
+      <c r="H39" s="86">
         <f t="shared" si="17"/>
         <v>15.01</v>
       </c>
-      <c r="I39" s="90">
+      <c r="I39" s="86">
         <f t="shared" si="17"/>
         <v>18.009999999999998</v>
       </c>
-      <c r="J39" s="90">
+      <c r="J39" s="86">
         <f t="shared" si="17"/>
         <v>21.009999999999998</v>
       </c>
-      <c r="K39" s="90">
+      <c r="K39" s="86">
         <f t="shared" si="17"/>
         <v>24.009999999999998</v>
       </c>
-      <c r="L39" s="90">
+      <c r="L39" s="86">
         <f t="shared" si="17"/>
         <v>27.009999999999998</v>
       </c>
-      <c r="M39" s="90">
+      <c r="M39" s="86">
         <f t="shared" si="17"/>
         <v>30.009999999999998</v>
       </c>
-      <c r="N39" s="90">
+      <c r="N39" s="86">
         <f t="shared" si="17"/>
         <v>33.01</v>
       </c>
-      <c r="O39" s="90">
+      <c r="O39" s="86">
         <f t="shared" si="17"/>
         <v>36.01</v>
       </c>
-      <c r="P39" s="90">
+      <c r="P39" s="86">
         <f t="shared" si="17"/>
         <v>39.01</v>
       </c>
-      <c r="Q39" s="90">
+      <c r="Q39" s="86">
         <f t="shared" si="17"/>
         <v>42.01</v>
       </c>
-      <c r="R39" s="90">
+      <c r="R39" s="86">
         <f t="shared" si="17"/>
         <v>45.01</v>
       </c>
-      <c r="S39" s="90">
+      <c r="S39" s="86">
         <f t="shared" si="17"/>
         <v>48.01</v>
       </c>
-      <c r="T39" s="94">
+      <c r="T39" s="90">
         <f t="shared" si="17"/>
         <v>51.01</v>
       </c>
-      <c r="U39" s="90">
+      <c r="U39" s="86">
         <f t="shared" si="17"/>
         <v>54.01</v>
       </c>
-      <c r="V39" s="90">
+      <c r="V39" s="86">
         <f t="shared" si="16"/>
         <v>57.01</v>
       </c>
-      <c r="W39" s="90">
+      <c r="W39" s="86">
         <f t="shared" si="16"/>
         <v>60.01</v>
       </c>
-      <c r="X39" s="90">
+      <c r="X39" s="86">
         <f t="shared" si="16"/>
         <v>63.01</v>
       </c>
-      <c r="Y39" s="90">
+      <c r="Y39" s="86">
         <f t="shared" si="16"/>
         <v>66.009999999999991</v>
       </c>
-      <c r="Z39" s="90">
+      <c r="Z39" s="86">
         <f t="shared" si="16"/>
         <v>69.009999999999991</v>
       </c>
-      <c r="AA39" s="90">
+      <c r="AA39" s="86">
         <f t="shared" si="16"/>
         <v>72.009999999999991</v>
       </c>
-      <c r="AB39" s="90">
+      <c r="AB39" s="86">
         <f t="shared" si="16"/>
         <v>75.009999999999991</v>
       </c>
-      <c r="AC39" s="90">
+      <c r="AC39" s="86">
         <f t="shared" si="16"/>
         <v>78.009999999999991</v>
       </c>
-      <c r="AD39" s="90">
+      <c r="AD39" s="86">
         <f t="shared" si="16"/>
         <v>81.009999999999991</v>
       </c>
@@ -6109,106 +6151,106 @@
       <c r="D40" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E40" s="90">
+      <c r="E40" s="86">
         <v>6.02</v>
       </c>
-      <c r="F40" s="90">
+      <c r="F40" s="86">
         <f t="shared" si="17"/>
         <v>9.02</v>
       </c>
-      <c r="G40" s="90">
+      <c r="G40" s="86">
         <f t="shared" si="16"/>
         <v>12.02</v>
       </c>
-      <c r="H40" s="90">
+      <c r="H40" s="86">
         <f t="shared" si="16"/>
         <v>15.02</v>
       </c>
-      <c r="I40" s="90">
+      <c r="I40" s="86">
         <f t="shared" si="16"/>
         <v>18.02</v>
       </c>
-      <c r="J40" s="90">
+      <c r="J40" s="86">
         <f t="shared" si="16"/>
         <v>21.02</v>
       </c>
-      <c r="K40" s="90">
+      <c r="K40" s="86">
         <f t="shared" si="16"/>
         <v>24.02</v>
       </c>
-      <c r="L40" s="90">
+      <c r="L40" s="86">
         <f t="shared" si="16"/>
         <v>27.02</v>
       </c>
-      <c r="M40" s="90">
+      <c r="M40" s="86">
         <f t="shared" si="16"/>
         <v>30.02</v>
       </c>
-      <c r="N40" s="90">
+      <c r="N40" s="86">
         <f t="shared" si="16"/>
         <v>33.019999999999996</v>
       </c>
-      <c r="O40" s="90">
+      <c r="O40" s="86">
         <f t="shared" si="16"/>
         <v>36.019999999999996</v>
       </c>
-      <c r="P40" s="90">
+      <c r="P40" s="86">
         <f t="shared" si="16"/>
         <v>39.019999999999996</v>
       </c>
-      <c r="Q40" s="90">
+      <c r="Q40" s="86">
         <f t="shared" si="16"/>
         <v>42.019999999999996</v>
       </c>
-      <c r="R40" s="90">
+      <c r="R40" s="86">
         <f t="shared" si="16"/>
         <v>45.019999999999996</v>
       </c>
-      <c r="S40" s="90">
+      <c r="S40" s="86">
         <f t="shared" si="16"/>
         <v>48.019999999999996</v>
       </c>
-      <c r="T40" s="94">
+      <c r="T40" s="90">
         <f t="shared" si="16"/>
         <v>51.019999999999996</v>
       </c>
-      <c r="U40" s="90">
+      <c r="U40" s="86">
         <f t="shared" si="16"/>
         <v>54.019999999999996</v>
       </c>
-      <c r="V40" s="90">
+      <c r="V40" s="86">
         <f t="shared" si="16"/>
         <v>57.019999999999996</v>
       </c>
-      <c r="W40" s="90">
+      <c r="W40" s="86">
         <f t="shared" si="16"/>
         <v>60.019999999999996</v>
       </c>
-      <c r="X40" s="90">
+      <c r="X40" s="86">
         <f t="shared" si="16"/>
         <v>63.019999999999996</v>
       </c>
-      <c r="Y40" s="90">
+      <c r="Y40" s="86">
         <f t="shared" si="16"/>
         <v>66.02</v>
       </c>
-      <c r="Z40" s="90">
+      <c r="Z40" s="86">
         <f t="shared" si="16"/>
         <v>69.02</v>
       </c>
-      <c r="AA40" s="90">
+      <c r="AA40" s="86">
         <f t="shared" si="16"/>
         <v>72.02</v>
       </c>
-      <c r="AB40" s="90">
+      <c r="AB40" s="86">
         <f t="shared" si="16"/>
         <v>75.02</v>
       </c>
-      <c r="AC40" s="90">
+      <c r="AC40" s="86">
         <f t="shared" si="16"/>
         <v>78.02</v>
       </c>
-      <c r="AD40" s="90">
+      <c r="AD40" s="86">
         <f t="shared" si="16"/>
         <v>81.02</v>
       </c>
@@ -6226,106 +6268,106 @@
       <c r="D41" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E41" s="90">
+      <c r="E41" s="86">
         <v>6.03</v>
       </c>
-      <c r="F41" s="90">
+      <c r="F41" s="86">
         <f t="shared" si="17"/>
         <v>9.0300000000000011</v>
       </c>
-      <c r="G41" s="90">
+      <c r="G41" s="86">
         <f t="shared" si="16"/>
         <v>12.030000000000001</v>
       </c>
-      <c r="H41" s="90">
+      <c r="H41" s="86">
         <f t="shared" si="16"/>
         <v>15.030000000000001</v>
       </c>
-      <c r="I41" s="90">
+      <c r="I41" s="86">
         <f t="shared" si="16"/>
         <v>18.03</v>
       </c>
-      <c r="J41" s="90">
+      <c r="J41" s="86">
         <f t="shared" si="16"/>
         <v>21.03</v>
       </c>
-      <c r="K41" s="90">
+      <c r="K41" s="86">
         <f t="shared" si="16"/>
         <v>24.03</v>
       </c>
-      <c r="L41" s="90">
+      <c r="L41" s="86">
         <f t="shared" si="16"/>
         <v>27.03</v>
       </c>
-      <c r="M41" s="90">
+      <c r="M41" s="86">
         <f t="shared" si="16"/>
         <v>30.03</v>
       </c>
-      <c r="N41" s="90">
+      <c r="N41" s="86">
         <f t="shared" si="16"/>
         <v>33.03</v>
       </c>
-      <c r="O41" s="90">
+      <c r="O41" s="86">
         <f t="shared" si="16"/>
         <v>36.03</v>
       </c>
-      <c r="P41" s="90">
+      <c r="P41" s="86">
         <f t="shared" si="16"/>
         <v>39.03</v>
       </c>
-      <c r="Q41" s="90">
+      <c r="Q41" s="86">
         <f t="shared" si="16"/>
         <v>42.03</v>
       </c>
-      <c r="R41" s="90">
+      <c r="R41" s="86">
         <f t="shared" si="16"/>
         <v>45.03</v>
       </c>
-      <c r="S41" s="90">
+      <c r="S41" s="86">
         <f t="shared" si="16"/>
         <v>48.03</v>
       </c>
-      <c r="T41" s="94">
+      <c r="T41" s="90">
         <f t="shared" si="16"/>
         <v>51.03</v>
       </c>
-      <c r="U41" s="90">
+      <c r="U41" s="86">
         <f t="shared" si="16"/>
         <v>54.03</v>
       </c>
-      <c r="V41" s="90">
+      <c r="V41" s="86">
         <f t="shared" si="16"/>
         <v>57.03</v>
       </c>
-      <c r="W41" s="90">
+      <c r="W41" s="86">
         <f t="shared" si="16"/>
         <v>60.03</v>
       </c>
-      <c r="X41" s="90">
+      <c r="X41" s="86">
         <f t="shared" si="16"/>
         <v>63.03</v>
       </c>
-      <c r="Y41" s="90">
+      <c r="Y41" s="86">
         <f t="shared" si="16"/>
         <v>66.03</v>
       </c>
-      <c r="Z41" s="90">
+      <c r="Z41" s="86">
         <f t="shared" si="16"/>
         <v>69.03</v>
       </c>
-      <c r="AA41" s="90">
+      <c r="AA41" s="86">
         <f t="shared" si="16"/>
         <v>72.03</v>
       </c>
-      <c r="AB41" s="90">
+      <c r="AB41" s="86">
         <f t="shared" si="16"/>
         <v>75.03</v>
       </c>
-      <c r="AC41" s="90">
+      <c r="AC41" s="86">
         <f t="shared" si="16"/>
         <v>78.03</v>
       </c>
-      <c r="AD41" s="90">
+      <c r="AD41" s="86">
         <f t="shared" si="16"/>
         <v>81.03</v>
       </c>
@@ -6343,106 +6385,106 @@
       <c r="D42" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E42" s="90">
+      <c r="E42" s="86">
         <v>6.04</v>
       </c>
-      <c r="F42" s="90">
+      <c r="F42" s="86">
         <f t="shared" si="17"/>
         <v>9.0399999999999991</v>
       </c>
-      <c r="G42" s="90">
+      <c r="G42" s="86">
         <f t="shared" si="16"/>
         <v>12.04</v>
       </c>
-      <c r="H42" s="90">
+      <c r="H42" s="86">
         <f t="shared" si="16"/>
         <v>15.04</v>
       </c>
-      <c r="I42" s="90">
+      <c r="I42" s="86">
         <f t="shared" si="16"/>
         <v>18.04</v>
       </c>
-      <c r="J42" s="90">
+      <c r="J42" s="86">
         <f t="shared" si="16"/>
         <v>21.04</v>
       </c>
-      <c r="K42" s="90">
+      <c r="K42" s="86">
         <f t="shared" si="16"/>
         <v>24.04</v>
       </c>
-      <c r="L42" s="90">
+      <c r="L42" s="86">
         <f t="shared" si="16"/>
         <v>27.04</v>
       </c>
-      <c r="M42" s="90">
+      <c r="M42" s="86">
         <f t="shared" si="16"/>
         <v>30.04</v>
       </c>
-      <c r="N42" s="90">
+      <c r="N42" s="86">
         <f t="shared" si="16"/>
         <v>33.04</v>
       </c>
-      <c r="O42" s="90">
+      <c r="O42" s="86">
         <f t="shared" si="16"/>
         <v>36.04</v>
       </c>
-      <c r="P42" s="90">
+      <c r="P42" s="86">
         <f t="shared" si="16"/>
         <v>39.04</v>
       </c>
-      <c r="Q42" s="90">
+      <c r="Q42" s="86">
         <f t="shared" si="16"/>
         <v>42.04</v>
       </c>
-      <c r="R42" s="90">
+      <c r="R42" s="86">
         <f t="shared" si="16"/>
         <v>45.04</v>
       </c>
-      <c r="S42" s="90">
+      <c r="S42" s="86">
         <f t="shared" si="16"/>
         <v>48.04</v>
       </c>
-      <c r="T42" s="94">
+      <c r="T42" s="90">
         <f t="shared" si="16"/>
         <v>51.04</v>
       </c>
-      <c r="U42" s="90">
+      <c r="U42" s="86">
         <f t="shared" si="16"/>
         <v>54.04</v>
       </c>
-      <c r="V42" s="90">
+      <c r="V42" s="86">
         <f t="shared" si="16"/>
         <v>57.04</v>
       </c>
-      <c r="W42" s="90">
+      <c r="W42" s="86">
         <f t="shared" si="16"/>
         <v>60.04</v>
       </c>
-      <c r="X42" s="90">
+      <c r="X42" s="86">
         <f t="shared" si="16"/>
         <v>63.04</v>
       </c>
-      <c r="Y42" s="90">
+      <c r="Y42" s="86">
         <f t="shared" si="16"/>
         <v>66.039999999999992</v>
       </c>
-      <c r="Z42" s="90">
+      <c r="Z42" s="86">
         <f t="shared" si="16"/>
         <v>69.039999999999992</v>
       </c>
-      <c r="AA42" s="90">
+      <c r="AA42" s="86">
         <f t="shared" si="16"/>
         <v>72.039999999999992</v>
       </c>
-      <c r="AB42" s="90">
+      <c r="AB42" s="86">
         <f t="shared" si="16"/>
         <v>75.039999999999992</v>
       </c>
-      <c r="AC42" s="90">
+      <c r="AC42" s="86">
         <f t="shared" si="16"/>
         <v>78.039999999999992</v>
       </c>
-      <c r="AD42" s="90">
+      <c r="AD42" s="86">
         <f t="shared" si="16"/>
         <v>81.039999999999992</v>
       </c>
@@ -6460,106 +6502,106 @@
       <c r="D43" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E43" s="90">
+      <c r="E43" s="86">
         <v>6.05</v>
       </c>
-      <c r="F43" s="90">
+      <c r="F43" s="86">
         <f t="shared" si="17"/>
         <v>9.0500000000000007</v>
       </c>
-      <c r="G43" s="90">
+      <c r="G43" s="86">
         <f t="shared" si="16"/>
         <v>12.05</v>
       </c>
-      <c r="H43" s="90">
+      <c r="H43" s="86">
         <f t="shared" si="16"/>
         <v>15.05</v>
       </c>
-      <c r="I43" s="90">
+      <c r="I43" s="86">
         <f t="shared" si="16"/>
         <v>18.05</v>
       </c>
-      <c r="J43" s="90">
+      <c r="J43" s="86">
         <f t="shared" si="16"/>
         <v>21.05</v>
       </c>
-      <c r="K43" s="90">
+      <c r="K43" s="86">
         <f t="shared" si="16"/>
         <v>24.05</v>
       </c>
-      <c r="L43" s="90">
+      <c r="L43" s="86">
         <f t="shared" si="16"/>
         <v>27.05</v>
       </c>
-      <c r="M43" s="90">
+      <c r="M43" s="86">
         <f t="shared" si="16"/>
         <v>30.05</v>
       </c>
-      <c r="N43" s="90">
+      <c r="N43" s="86">
         <f t="shared" si="16"/>
         <v>33.049999999999997</v>
       </c>
-      <c r="O43" s="90">
+      <c r="O43" s="86">
         <f t="shared" si="16"/>
         <v>36.049999999999997</v>
       </c>
-      <c r="P43" s="90">
+      <c r="P43" s="86">
         <f t="shared" si="16"/>
         <v>39.049999999999997</v>
       </c>
-      <c r="Q43" s="90">
+      <c r="Q43" s="86">
         <f t="shared" si="16"/>
         <v>42.05</v>
       </c>
-      <c r="R43" s="90">
+      <c r="R43" s="86">
         <f t="shared" si="16"/>
         <v>45.05</v>
       </c>
-      <c r="S43" s="90">
+      <c r="S43" s="86">
         <f t="shared" si="16"/>
         <v>48.05</v>
       </c>
-      <c r="T43" s="94">
+      <c r="T43" s="90">
         <f t="shared" si="16"/>
         <v>51.05</v>
       </c>
-      <c r="U43" s="90">
+      <c r="U43" s="86">
         <f t="shared" si="16"/>
         <v>54.05</v>
       </c>
-      <c r="V43" s="90">
+      <c r="V43" s="86">
         <f t="shared" si="16"/>
         <v>57.05</v>
       </c>
-      <c r="W43" s="90">
+      <c r="W43" s="86">
         <f t="shared" si="16"/>
         <v>60.05</v>
       </c>
-      <c r="X43" s="90">
+      <c r="X43" s="86">
         <f t="shared" si="16"/>
         <v>63.05</v>
       </c>
-      <c r="Y43" s="90">
+      <c r="Y43" s="86">
         <f t="shared" si="16"/>
         <v>66.05</v>
       </c>
-      <c r="Z43" s="90">
+      <c r="Z43" s="86">
         <f t="shared" si="16"/>
         <v>69.05</v>
       </c>
-      <c r="AA43" s="90">
+      <c r="AA43" s="86">
         <f t="shared" si="16"/>
         <v>72.05</v>
       </c>
-      <c r="AB43" s="90">
+      <c r="AB43" s="86">
         <f t="shared" si="16"/>
         <v>75.05</v>
       </c>
-      <c r="AC43" s="90">
+      <c r="AC43" s="86">
         <f t="shared" si="16"/>
         <v>78.05</v>
       </c>
-      <c r="AD43" s="90">
+      <c r="AD43" s="86">
         <f t="shared" si="16"/>
         <v>81.05</v>
       </c>
@@ -6572,7 +6614,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3049BD40-9D77-4237-9F54-D8C44070C0CD}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A2:L117"/>
+  <dimension ref="A2:L123"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="20.6328125" style="29" bestFit="1" customWidth="1"/>
@@ -6632,19 +6674,19 @@
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A5" s="59" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="60" t="s">
+      <c r="A5" s="107" t="s">
+        <v>199</v>
+      </c>
+      <c r="B5" s="108" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="61" t="s">
+      <c r="C5" s="109" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="42" t="s">
+      <c r="D5" s="80" t="s">
         <v>50</v>
       </c>
-      <c r="E5" s="44">
+      <c r="E5" s="82">
         <v>0</v>
       </c>
       <c r="F5" s="28"/>
@@ -6658,27 +6700,27 @@
       <c r="J5" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="K5" s="57">
+      <c r="K5" s="56">
         <v>0</v>
       </c>
-      <c r="L5" s="56">
+      <c r="L5" s="55">
         <v>1000</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A6" s="41" t="s">
+      <c r="A6" s="79" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="42" t="s">
+      <c r="B6" s="80" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="43" t="s">
+      <c r="C6" s="81" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="42" t="s">
+      <c r="D6" s="80" t="s">
         <v>50</v>
       </c>
-      <c r="E6" s="44">
+      <c r="E6" s="82">
         <v>10</v>
       </c>
       <c r="F6" s="28"/>
@@ -6697,21 +6739,11 @@
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A7" s="41" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="42" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="43" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" s="42" t="s">
-        <v>50</v>
-      </c>
-      <c r="E7" s="44">
-        <v>20</v>
-      </c>
+      <c r="A7" s="105"/>
+      <c r="B7" s="103"/>
+      <c r="C7" s="106"/>
+      <c r="D7" s="103"/>
+      <c r="E7" s="104"/>
       <c r="F7" s="28"/>
       <c r="G7" s="28"/>
       <c r="H7" s="29" t="s">
@@ -6728,19 +6760,19 @@
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A8" s="83" t="s">
+      <c r="A8" s="79" t="s">
         <v>83</v>
       </c>
-      <c r="B8" s="84" t="s">
+      <c r="B8" s="80" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="85" t="s">
+      <c r="C8" s="81" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="84" t="s">
+      <c r="D8" s="80" t="s">
         <v>50</v>
       </c>
-      <c r="E8" s="86">
+      <c r="E8" s="82">
         <v>30</v>
       </c>
       <c r="F8" s="28"/>
@@ -6857,19 +6889,19 @@
       </c>
       <c r="F12" s="28"/>
       <c r="G12" s="28"/>
-      <c r="H12" s="75" t="s">
+      <c r="H12" s="71" t="s">
         <v>106</v>
       </c>
-      <c r="I12" s="76" t="s">
+      <c r="I12" s="72" t="s">
         <v>16</v>
       </c>
-      <c r="J12" s="77" t="s">
+      <c r="J12" s="73" t="s">
         <v>19</v>
       </c>
-      <c r="K12" s="78">
+      <c r="K12" s="74">
         <v>0</v>
       </c>
-      <c r="L12" s="55">
+      <c r="L12" s="54">
         <v>5</v>
       </c>
     </row>
@@ -6888,16 +6920,16 @@
       </c>
       <c r="F13" s="28"/>
       <c r="G13" s="28"/>
-      <c r="H13" s="84" t="s">
+      <c r="H13" s="80" t="s">
         <v>126</v>
       </c>
-      <c r="I13" s="84" t="s">
+      <c r="I13" s="80" t="s">
         <v>16</v>
       </c>
-      <c r="J13" s="86" t="s">
+      <c r="J13" s="82" t="s">
         <v>19</v>
       </c>
-      <c r="K13" s="89">
+      <c r="K13" s="85">
         <v>1</v>
       </c>
       <c r="L13" s="28"/>
@@ -6917,19 +6949,19 @@
       <c r="J14" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="K14" s="53">
+      <c r="K14" s="52">
         <v>3</v>
       </c>
       <c r="L14" s="28"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A15" s="45" t="s">
+      <c r="A15" s="44" t="s">
         <v>105</v>
       </c>
-      <c r="B15" s="46" t="s">
+      <c r="B15" s="45" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="47" t="s">
+      <c r="C15" s="46" t="s">
         <v>18</v>
       </c>
       <c r="E15" s="28">
@@ -6949,13 +6981,13 @@
       <c r="L15" s="28"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A16" s="48" t="s">
+      <c r="A16" s="47" t="s">
         <v>104</v>
       </c>
       <c r="B16" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="49" t="s">
+      <c r="C16" s="48" t="s">
         <v>18</v>
       </c>
       <c r="E16" s="28">
@@ -6975,13 +7007,13 @@
       <c r="L16" s="28"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A17" s="48" t="s">
+      <c r="A17" s="47" t="s">
         <v>103</v>
       </c>
       <c r="B17" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="C17" s="49" t="s">
+      <c r="C17" s="48" t="s">
         <v>18</v>
       </c>
       <c r="E17" s="28">
@@ -7001,8 +7033,8 @@
       <c r="L17" s="28"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A18" s="48"/>
-      <c r="C18" s="49"/>
+      <c r="A18" s="47"/>
+      <c r="C18" s="48"/>
       <c r="E18" s="28"/>
       <c r="F18" s="28"/>
       <c r="G18" s="28"/>
@@ -7015,12 +7047,14 @@
       <c r="J18" s="28" t="s">
         <v>123</v>
       </c>
-      <c r="K18" s="54">
+      <c r="K18" s="53">
         <v>0</v>
       </c>
       <c r="L18" s="28"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="C19" s="28"/>
+      <c r="E19" s="28"/>
       <c r="F19" s="28"/>
       <c r="G19" s="28"/>
       <c r="H19" s="29" t="s">
@@ -7038,19 +7072,8 @@
       <c r="L19" s="28"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A20" s="83" t="s">
-        <v>102</v>
-      </c>
-      <c r="B20" s="84" t="s">
-        <v>13</v>
-      </c>
-      <c r="C20" s="85" t="s">
-        <v>18</v>
-      </c>
-      <c r="D20" s="84"/>
-      <c r="E20" s="86">
-        <v>110</v>
-      </c>
+      <c r="C20" s="28"/>
+      <c r="E20" s="28"/>
       <c r="F20" s="28"/>
       <c r="G20" s="28"/>
       <c r="H20" s="29" t="s">
@@ -7068,18 +7091,8 @@
       <c r="L20" s="28"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A21" s="39" t="s">
-        <v>171</v>
-      </c>
-      <c r="B21" s="29" t="s">
-        <v>13</v>
-      </c>
-      <c r="C21" s="40" t="s">
-        <v>18</v>
-      </c>
-      <c r="E21" s="28">
-        <v>115</v>
-      </c>
+      <c r="C21" s="28"/>
+      <c r="E21" s="28"/>
       <c r="F21" s="28"/>
       <c r="G21" s="28"/>
       <c r="H21" s="29" t="s">
@@ -7097,19 +7110,6 @@
       <c r="L21" s="28"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A22" s="83" t="s">
-        <v>101</v>
-      </c>
-      <c r="B22" s="84" t="s">
-        <v>13</v>
-      </c>
-      <c r="C22" s="85" t="s">
-        <v>18</v>
-      </c>
-      <c r="D22" s="84"/>
-      <c r="E22" s="86">
-        <v>120</v>
-      </c>
       <c r="F22" s="28"/>
       <c r="G22" s="28"/>
       <c r="H22" s="29" t="s">
@@ -7127,17 +7127,18 @@
       <c r="L22" s="28"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A23" s="39" t="s">
-        <v>112</v>
-      </c>
-      <c r="B23" s="29" t="s">
+      <c r="A23" s="79" t="s">
+        <v>102</v>
+      </c>
+      <c r="B23" s="80" t="s">
         <v>13</v>
       </c>
-      <c r="C23" s="40" t="s">
+      <c r="C23" s="81" t="s">
         <v>18</v>
       </c>
-      <c r="E23" s="28">
-        <v>125</v>
+      <c r="D23" s="80"/>
+      <c r="E23" s="82">
+        <v>110</v>
       </c>
       <c r="F23" s="28"/>
       <c r="G23" s="28"/>
@@ -7157,7 +7158,7 @@
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A24" s="39" t="s">
-        <v>100</v>
+        <v>171</v>
       </c>
       <c r="B24" s="29" t="s">
         <v>13</v>
@@ -7166,7 +7167,7 @@
         <v>18</v>
       </c>
       <c r="E24" s="28">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="F24" s="28"/>
       <c r="G24" s="28"/>
@@ -7185,17 +7186,18 @@
       <c r="L24" s="28"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A25" s="39" t="s">
-        <v>175</v>
-      </c>
-      <c r="B25" s="29" t="s">
+      <c r="A25" s="79" t="s">
+        <v>101</v>
+      </c>
+      <c r="B25" s="80" t="s">
         <v>13</v>
       </c>
-      <c r="C25" s="40" t="s">
+      <c r="C25" s="81" t="s">
         <v>18</v>
       </c>
-      <c r="E25" s="28">
-        <v>140</v>
+      <c r="D25" s="80"/>
+      <c r="E25" s="82">
+        <v>120</v>
       </c>
       <c r="F25" s="28"/>
       <c r="G25" s="28"/>
@@ -7214,9 +7216,18 @@
       <c r="L25" s="28"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A26" s="39"/>
-      <c r="C26" s="28"/>
-      <c r="E26" s="28"/>
+      <c r="A26" s="39" t="s">
+        <v>112</v>
+      </c>
+      <c r="B26" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="C26" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="E26" s="28">
+        <v>125</v>
+      </c>
       <c r="F26" s="28"/>
       <c r="G26" s="28"/>
       <c r="H26" s="29" t="s">
@@ -7234,9 +7245,18 @@
       <c r="L26" s="28"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A27" s="39"/>
-      <c r="C27" s="28"/>
-      <c r="E27" s="28"/>
+      <c r="A27" s="39" t="s">
+        <v>100</v>
+      </c>
+      <c r="B27" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="C27" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="E27" s="28">
+        <v>130</v>
+      </c>
       <c r="F27" s="28"/>
       <c r="G27" s="28"/>
       <c r="H27" s="29" t="s">
@@ -7254,9 +7274,18 @@
       <c r="L27" s="28"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A28" s="39"/>
-      <c r="C28" s="28"/>
-      <c r="E28" s="28"/>
+      <c r="A28" s="39" t="s">
+        <v>175</v>
+      </c>
+      <c r="B28" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="C28" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="E28" s="28">
+        <v>140</v>
+      </c>
       <c r="F28" s="28"/>
       <c r="G28" s="28"/>
       <c r="H28" s="29" t="s">
@@ -7294,18 +7323,9 @@
       <c r="L29" s="28"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A30" s="39" t="s">
-        <v>107</v>
-      </c>
-      <c r="B30" s="29" t="s">
-        <v>13</v>
-      </c>
-      <c r="C30" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="E30" s="28">
-        <v>190</v>
-      </c>
+      <c r="A30" s="39"/>
+      <c r="C30" s="28"/>
+      <c r="E30" s="28"/>
       <c r="F30" s="28"/>
       <c r="G30" s="28"/>
       <c r="H30" s="29" t="s">
@@ -7323,21 +7343,9 @@
       <c r="L30" s="28"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A31" s="83" t="s">
-        <v>6</v>
-      </c>
-      <c r="B31" s="84" t="s">
-        <v>15</v>
-      </c>
-      <c r="C31" s="85" t="s">
-        <v>18</v>
-      </c>
-      <c r="D31" s="84" t="s">
-        <v>50</v>
-      </c>
-      <c r="E31" s="86">
-        <v>200</v>
-      </c>
+      <c r="A31" s="39"/>
+      <c r="C31" s="28"/>
+      <c r="E31" s="28"/>
       <c r="F31" s="28"/>
       <c r="G31" s="28"/>
       <c r="H31" s="29" t="s">
@@ -7355,20 +7363,20 @@
       <c r="L31" s="28"/>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A32" s="83" t="s">
-        <v>7</v>
-      </c>
-      <c r="B32" s="84" t="s">
-        <v>15</v>
-      </c>
-      <c r="C32" s="85" t="s">
+      <c r="A32" s="41" t="s">
+        <v>200</v>
+      </c>
+      <c r="B32" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="C32" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="D32" s="84" t="s">
-        <v>50</v>
-      </c>
-      <c r="E32" s="86">
-        <v>300</v>
+      <c r="D32" s="42" t="s">
+        <v>115</v>
+      </c>
+      <c r="E32" s="43">
+        <v>180</v>
       </c>
       <c r="F32" s="28"/>
       <c r="G32" s="28"/>
@@ -7387,20 +7395,20 @@
       <c r="L32" s="28"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A33" s="39" t="s">
-        <v>102</v>
-      </c>
-      <c r="B33" s="29" t="s">
-        <v>15</v>
-      </c>
-      <c r="C33" s="28" t="s">
+      <c r="A33" s="41" t="s">
+        <v>107</v>
+      </c>
+      <c r="B33" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="C33" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="D33" s="29" t="s">
+      <c r="D33" s="42" t="s">
         <v>115</v>
       </c>
-      <c r="E33" s="28">
-        <v>400</v>
+      <c r="E33" s="43">
+        <v>190</v>
       </c>
       <c r="F33" s="28"/>
       <c r="G33" s="28"/>
@@ -7419,20 +7427,20 @@
       <c r="L33" s="28"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A34" s="39" t="s">
-        <v>79</v>
-      </c>
-      <c r="B34" s="29" t="s">
-        <v>80</v>
-      </c>
-      <c r="C34" s="28" t="s">
+      <c r="A34" s="79" t="s">
+        <v>6</v>
+      </c>
+      <c r="B34" s="80" t="s">
+        <v>15</v>
+      </c>
+      <c r="C34" s="81" t="s">
         <v>18</v>
       </c>
-      <c r="D34" s="29" t="s">
-        <v>115</v>
-      </c>
-      <c r="E34" s="28">
-        <v>500</v>
+      <c r="D34" s="80" t="s">
+        <v>50</v>
+      </c>
+      <c r="E34" s="82">
+        <v>200</v>
       </c>
       <c r="F34" s="28"/>
       <c r="G34" s="28"/>
@@ -7451,18 +7459,20 @@
       <c r="L34" s="28"/>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A35" s="45" t="s">
-        <v>108</v>
-      </c>
-      <c r="B35" s="46" t="s">
-        <v>14</v>
-      </c>
-      <c r="C35" s="62" t="s">
-        <v>123</v>
-      </c>
-      <c r="D35" s="46"/>
-      <c r="E35" s="47">
-        <v>0</v>
+      <c r="A35" s="79" t="s">
+        <v>7</v>
+      </c>
+      <c r="B35" s="80" t="s">
+        <v>15</v>
+      </c>
+      <c r="C35" s="81" t="s">
+        <v>18</v>
+      </c>
+      <c r="D35" s="80" t="s">
+        <v>50</v>
+      </c>
+      <c r="E35" s="82">
+        <v>300</v>
       </c>
       <c r="F35" s="28"/>
       <c r="G35" s="28"/>
@@ -7481,17 +7491,20 @@
       <c r="L35" s="28"/>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A36" s="48" t="s">
-        <v>148</v>
-      </c>
-      <c r="B36" s="29" t="s">
-        <v>151</v>
-      </c>
-      <c r="C36" s="28" t="s">
-        <v>123</v>
-      </c>
-      <c r="E36" s="49">
-        <v>5</v>
+      <c r="A36" s="41" t="s">
+        <v>102</v>
+      </c>
+      <c r="B36" s="42" t="s">
+        <v>15</v>
+      </c>
+      <c r="C36" s="43" t="s">
+        <v>18</v>
+      </c>
+      <c r="D36" s="42" t="s">
+        <v>115</v>
+      </c>
+      <c r="E36" s="43">
+        <v>400</v>
       </c>
       <c r="F36" s="28"/>
       <c r="G36" s="28"/>
@@ -7510,17 +7523,20 @@
       <c r="L36" s="28"/>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A37" s="48" t="s">
-        <v>149</v>
-      </c>
-      <c r="B37" s="29" t="s">
-        <v>14</v>
-      </c>
-      <c r="C37" s="28" t="s">
-        <v>123</v>
-      </c>
-      <c r="E37" s="49">
-        <v>10</v>
+      <c r="A37" s="41" t="s">
+        <v>79</v>
+      </c>
+      <c r="B37" s="42" t="s">
+        <v>80</v>
+      </c>
+      <c r="C37" s="43" t="s">
+        <v>18</v>
+      </c>
+      <c r="D37" s="42" t="s">
+        <v>115</v>
+      </c>
+      <c r="E37" s="43">
+        <v>500</v>
       </c>
       <c r="F37" s="28"/>
       <c r="G37" s="28"/>
@@ -7539,17 +7555,18 @@
       <c r="L37" s="28"/>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A38" s="48" t="s">
-        <v>150</v>
-      </c>
-      <c r="B38" s="29" t="s">
-        <v>15</v>
-      </c>
-      <c r="C38" s="28" t="s">
+      <c r="A38" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="B38" s="45" t="s">
+        <v>14</v>
+      </c>
+      <c r="C38" s="58" t="s">
         <v>123</v>
       </c>
-      <c r="E38" s="49">
-        <v>15</v>
+      <c r="D38" s="45"/>
+      <c r="E38" s="46">
+        <v>0</v>
       </c>
       <c r="F38" s="28"/>
       <c r="G38" s="28"/>
@@ -7568,18 +7585,17 @@
       <c r="L38" s="28"/>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A39" s="50" t="s">
-        <v>153</v>
-      </c>
-      <c r="B39" s="51" t="s">
-        <v>13</v>
-      </c>
-      <c r="C39" s="63" t="s">
+      <c r="A39" s="47" t="s">
+        <v>148</v>
+      </c>
+      <c r="B39" s="29" t="s">
+        <v>151</v>
+      </c>
+      <c r="C39" s="28" t="s">
         <v>123</v>
       </c>
-      <c r="D39" s="51"/>
-      <c r="E39" s="52">
-        <v>20</v>
+      <c r="E39" s="48">
+        <v>5</v>
       </c>
       <c r="F39" s="28"/>
       <c r="G39" s="28"/>
@@ -7598,18 +7614,17 @@
       <c r="L39" s="28"/>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A40" s="87" t="s">
-        <v>63</v>
-      </c>
-      <c r="B40" s="84" t="s">
+      <c r="A40" s="47" t="s">
+        <v>149</v>
+      </c>
+      <c r="B40" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="C40" s="88" t="s">
-        <v>18</v>
-      </c>
-      <c r="D40" s="84"/>
-      <c r="E40" s="86">
-        <v>740</v>
+      <c r="C40" s="28" t="s">
+        <v>123</v>
+      </c>
+      <c r="E40" s="48">
+        <v>10</v>
       </c>
       <c r="F40" s="28"/>
       <c r="G40" s="28"/>
@@ -7628,18 +7643,17 @@
       <c r="L40" s="28"/>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A41" s="87" t="s">
-        <v>64</v>
-      </c>
-      <c r="B41" s="84" t="s">
-        <v>14</v>
-      </c>
-      <c r="C41" s="88" t="s">
-        <v>18</v>
-      </c>
-      <c r="D41" s="84"/>
-      <c r="E41" s="86">
-        <v>745</v>
+      <c r="A41" s="47" t="s">
+        <v>150</v>
+      </c>
+      <c r="B41" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="C41" s="28" t="s">
+        <v>123</v>
+      </c>
+      <c r="E41" s="48">
+        <v>15</v>
       </c>
       <c r="F41" s="28"/>
       <c r="G41" s="28"/>
@@ -7658,18 +7672,18 @@
       <c r="L41" s="28"/>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A42" s="87" t="s">
-        <v>65</v>
-      </c>
-      <c r="B42" s="84" t="s">
-        <v>14</v>
-      </c>
-      <c r="C42" s="88" t="s">
-        <v>18</v>
-      </c>
-      <c r="D42" s="84"/>
-      <c r="E42" s="86">
-        <v>750</v>
+      <c r="A42" s="49" t="s">
+        <v>153</v>
+      </c>
+      <c r="B42" s="50" t="s">
+        <v>13</v>
+      </c>
+      <c r="C42" s="59" t="s">
+        <v>123</v>
+      </c>
+      <c r="D42" s="50"/>
+      <c r="E42" s="51">
+        <v>20</v>
       </c>
       <c r="F42" s="28"/>
       <c r="G42" s="28"/>
@@ -7688,18 +7702,17 @@
       <c r="L42" s="28"/>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A43" s="87" t="s">
-        <v>66</v>
-      </c>
-      <c r="B43" s="84" t="s">
-        <v>14</v>
-      </c>
-      <c r="C43" s="88" t="s">
-        <v>18</v>
-      </c>
-      <c r="D43" s="84"/>
-      <c r="E43" s="86">
-        <v>755</v>
+      <c r="A43" s="47" t="s">
+        <v>196</v>
+      </c>
+      <c r="B43" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="C43" s="28" t="s">
+        <v>123</v>
+      </c>
+      <c r="E43" s="28">
+        <v>30</v>
       </c>
       <c r="F43" s="28"/>
       <c r="G43" s="28"/>
@@ -7718,18 +7731,17 @@
       <c r="L43" s="28"/>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A44" s="87" t="s">
-        <v>67</v>
-      </c>
-      <c r="B44" s="84" t="s">
-        <v>14</v>
-      </c>
-      <c r="C44" s="88" t="s">
-        <v>18</v>
-      </c>
-      <c r="D44" s="84"/>
-      <c r="E44" s="86">
-        <v>760</v>
+      <c r="A44" s="47" t="s">
+        <v>197</v>
+      </c>
+      <c r="B44" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="C44" s="28" t="s">
+        <v>123</v>
+      </c>
+      <c r="E44" s="28">
+        <v>32</v>
       </c>
       <c r="F44" s="28"/>
       <c r="G44" s="28"/>
@@ -7748,1322 +7760,1441 @@
       <c r="L44" s="28"/>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A45" s="87" t="s">
-        <v>68</v>
-      </c>
-      <c r="B45" s="84" t="s">
-        <v>14</v>
-      </c>
-      <c r="C45" s="88" t="s">
-        <v>18</v>
-      </c>
-      <c r="D45" s="84"/>
-      <c r="E45" s="86">
-        <v>765</v>
+      <c r="A45" s="47" t="s">
+        <v>198</v>
+      </c>
+      <c r="B45" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="C45" s="28" t="s">
+        <v>123</v>
+      </c>
+      <c r="E45" s="28">
+        <v>34</v>
       </c>
       <c r="F45" s="28"/>
       <c r="G45" s="28"/>
+      <c r="J45" s="29"/>
+      <c r="K45" s="29"/>
       <c r="L45" s="28"/>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A46" s="87" t="s">
-        <v>69</v>
-      </c>
-      <c r="B46" s="84" t="s">
+      <c r="A46" s="83" t="s">
+        <v>63</v>
+      </c>
+      <c r="B46" s="80" t="s">
         <v>14</v>
       </c>
-      <c r="C46" s="88" t="s">
+      <c r="C46" s="84" t="s">
         <v>18</v>
       </c>
-      <c r="D46" s="84"/>
-      <c r="E46" s="86">
-        <v>770</v>
+      <c r="D46" s="80"/>
+      <c r="E46" s="82">
+        <v>740</v>
       </c>
       <c r="F46" s="28"/>
       <c r="G46" s="28"/>
+      <c r="J46" s="29"/>
+      <c r="K46" s="29"/>
       <c r="L46" s="28"/>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A47" s="87" t="s">
-        <v>70</v>
-      </c>
-      <c r="B47" s="84" t="s">
+      <c r="A47" s="83" t="s">
+        <v>64</v>
+      </c>
+      <c r="B47" s="80" t="s">
         <v>14</v>
       </c>
-      <c r="C47" s="88" t="s">
+      <c r="C47" s="84" t="s">
         <v>18</v>
       </c>
-      <c r="D47" s="84"/>
-      <c r="E47" s="86">
-        <v>775</v>
+      <c r="D47" s="80"/>
+      <c r="E47" s="82">
+        <v>745</v>
       </c>
       <c r="F47" s="28"/>
       <c r="G47" s="28"/>
+      <c r="J47" s="29"/>
+      <c r="K47" s="29"/>
       <c r="L47" s="28"/>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A48" s="48"/>
-      <c r="C48" s="49"/>
-      <c r="E48" s="28"/>
+      <c r="A48" s="83" t="s">
+        <v>65</v>
+      </c>
+      <c r="B48" s="80" t="s">
+        <v>14</v>
+      </c>
+      <c r="C48" s="84" t="s">
+        <v>18</v>
+      </c>
+      <c r="D48" s="80"/>
+      <c r="E48" s="82">
+        <v>750</v>
+      </c>
       <c r="F48" s="28"/>
       <c r="G48" s="28"/>
+      <c r="J48" s="29"/>
+      <c r="K48" s="29"/>
       <c r="L48" s="28"/>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A49" s="48"/>
-      <c r="C49" s="49"/>
-      <c r="E49" s="28"/>
+      <c r="A49" s="83" t="s">
+        <v>66</v>
+      </c>
+      <c r="B49" s="80" t="s">
+        <v>14</v>
+      </c>
+      <c r="C49" s="84" t="s">
+        <v>18</v>
+      </c>
+      <c r="D49" s="80"/>
+      <c r="E49" s="82">
+        <v>755</v>
+      </c>
       <c r="F49" s="28"/>
       <c r="G49" s="28"/>
+      <c r="J49" s="29"/>
+      <c r="K49" s="29"/>
       <c r="L49" s="28"/>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A50" s="50"/>
-      <c r="B50" s="51"/>
-      <c r="C50" s="52"/>
-      <c r="E50" s="28"/>
+      <c r="A50" s="83" t="s">
+        <v>67</v>
+      </c>
+      <c r="B50" s="80" t="s">
+        <v>14</v>
+      </c>
+      <c r="C50" s="84" t="s">
+        <v>18</v>
+      </c>
+      <c r="D50" s="80"/>
+      <c r="E50" s="82">
+        <v>760</v>
+      </c>
       <c r="F50" s="28"/>
       <c r="G50" s="28"/>
+      <c r="J50" s="29"/>
+      <c r="K50" s="29"/>
       <c r="L50" s="28"/>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A51" s="48" t="s">
-        <v>71</v>
-      </c>
-      <c r="B51" s="29" t="s">
+      <c r="A51" s="83" t="s">
+        <v>68</v>
+      </c>
+      <c r="B51" s="80" t="s">
         <v>14</v>
       </c>
-      <c r="C51" s="49" t="s">
+      <c r="C51" s="84" t="s">
         <v>18</v>
       </c>
-      <c r="E51" s="28">
-        <v>700</v>
+      <c r="D51" s="80"/>
+      <c r="E51" s="82">
+        <v>765</v>
       </c>
       <c r="F51" s="28"/>
       <c r="G51" s="28"/>
       <c r="L51" s="28"/>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A52" s="48" t="s">
-        <v>72</v>
-      </c>
-      <c r="B52" s="29" t="s">
+      <c r="A52" s="83" t="s">
+        <v>69</v>
+      </c>
+      <c r="B52" s="80" t="s">
         <v>14</v>
       </c>
-      <c r="C52" s="49" t="s">
+      <c r="C52" s="84" t="s">
         <v>18</v>
       </c>
-      <c r="E52" s="28">
-        <v>705</v>
+      <c r="D52" s="80"/>
+      <c r="E52" s="82">
+        <v>770</v>
       </c>
       <c r="F52" s="28"/>
       <c r="G52" s="28"/>
       <c r="L52" s="28"/>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A53" s="48" t="s">
-        <v>73</v>
-      </c>
-      <c r="B53" s="29" t="s">
+      <c r="A53" s="83" t="s">
+        <v>70</v>
+      </c>
+      <c r="B53" s="80" t="s">
         <v>14</v>
       </c>
-      <c r="C53" s="49" t="s">
+      <c r="C53" s="84" t="s">
         <v>18</v>
       </c>
-      <c r="E53" s="28">
-        <v>710</v>
+      <c r="D53" s="80"/>
+      <c r="E53" s="82">
+        <v>775</v>
       </c>
       <c r="F53" s="28"/>
       <c r="G53" s="28"/>
       <c r="L53" s="28"/>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A54" s="48" t="s">
-        <v>74</v>
-      </c>
-      <c r="B54" s="29" t="s">
-        <v>14</v>
-      </c>
-      <c r="C54" s="49" t="s">
-        <v>18</v>
-      </c>
-      <c r="E54" s="28">
-        <v>715</v>
-      </c>
+      <c r="A54" s="47"/>
+      <c r="C54" s="48"/>
+      <c r="E54" s="28"/>
       <c r="F54" s="28"/>
       <c r="G54" s="28"/>
       <c r="L54" s="28"/>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A55" s="48" t="s">
-        <v>75</v>
-      </c>
-      <c r="B55" s="29" t="s">
-        <v>14</v>
-      </c>
-      <c r="C55" s="49" t="s">
-        <v>18</v>
-      </c>
-      <c r="E55" s="28">
-        <v>720</v>
-      </c>
+      <c r="A55" s="47"/>
+      <c r="C55" s="48"/>
+      <c r="E55" s="28"/>
       <c r="F55" s="28"/>
       <c r="G55" s="28"/>
       <c r="L55" s="28"/>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A56" s="48" t="s">
-        <v>76</v>
-      </c>
-      <c r="B56" s="29" t="s">
-        <v>14</v>
-      </c>
-      <c r="C56" s="49" t="s">
-        <v>18</v>
-      </c>
-      <c r="E56" s="28">
-        <v>725</v>
-      </c>
+      <c r="A56" s="49"/>
+      <c r="B56" s="50"/>
+      <c r="C56" s="51"/>
+      <c r="E56" s="28"/>
       <c r="F56" s="28"/>
       <c r="G56" s="28"/>
       <c r="L56" s="28"/>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A57" s="48" t="s">
-        <v>77</v>
+      <c r="A57" s="47" t="s">
+        <v>71</v>
       </c>
       <c r="B57" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="C57" s="49" t="s">
+      <c r="C57" s="48" t="s">
         <v>18</v>
       </c>
       <c r="E57" s="28">
-        <v>730</v>
+        <v>700</v>
       </c>
       <c r="F57" s="28"/>
       <c r="G57" s="28"/>
       <c r="L57" s="28"/>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A58" s="48" t="s">
-        <v>78</v>
+      <c r="A58" s="47" t="s">
+        <v>72</v>
       </c>
       <c r="B58" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="C58" s="49" t="s">
+      <c r="C58" s="48" t="s">
         <v>18</v>
       </c>
       <c r="E58" s="28">
-        <v>735</v>
+        <v>705</v>
       </c>
       <c r="F58" s="28"/>
       <c r="G58" s="28"/>
       <c r="L58" s="28"/>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A59" s="48"/>
-      <c r="C59" s="49"/>
-      <c r="E59" s="28"/>
+      <c r="A59" s="47" t="s">
+        <v>73</v>
+      </c>
+      <c r="B59" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="C59" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="E59" s="28">
+        <v>710</v>
+      </c>
       <c r="F59" s="28"/>
       <c r="G59" s="28"/>
       <c r="L59" s="28"/>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A60" s="48"/>
-      <c r="C60" s="49"/>
-      <c r="E60" s="28"/>
+      <c r="A60" s="47" t="s">
+        <v>74</v>
+      </c>
+      <c r="B60" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="C60" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="E60" s="28">
+        <v>715</v>
+      </c>
       <c r="F60" s="28"/>
       <c r="G60" s="28"/>
       <c r="L60" s="28"/>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A61" s="48"/>
-      <c r="C61" s="49"/>
-      <c r="E61" s="28"/>
+      <c r="A61" s="47" t="s">
+        <v>75</v>
+      </c>
+      <c r="B61" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="C61" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="E61" s="28">
+        <v>720</v>
+      </c>
       <c r="F61" s="28"/>
       <c r="G61" s="28"/>
       <c r="L61" s="28"/>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A62" s="87" t="s">
-        <v>85</v>
-      </c>
-      <c r="B62" s="84" t="s">
-        <v>13</v>
-      </c>
-      <c r="C62" s="88" t="s">
+      <c r="A62" s="47" t="s">
+        <v>76</v>
+      </c>
+      <c r="B62" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="C62" s="48" t="s">
         <v>18</v>
       </c>
-      <c r="D62" s="84" t="s">
-        <v>50</v>
-      </c>
-      <c r="E62" s="86">
-        <v>1000</v>
+      <c r="E62" s="28">
+        <v>725</v>
       </c>
       <c r="F62" s="28"/>
       <c r="G62" s="28"/>
       <c r="L62" s="28"/>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A63" s="45" t="s">
+      <c r="A63" s="47" t="s">
+        <v>77</v>
+      </c>
+      <c r="B63" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="C63" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="E63" s="28">
+        <v>730</v>
+      </c>
+      <c r="F63" s="28"/>
+      <c r="G63" s="28"/>
+      <c r="L63" s="28"/>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A64" s="47" t="s">
+        <v>78</v>
+      </c>
+      <c r="B64" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="C64" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="E64" s="28">
+        <v>735</v>
+      </c>
+      <c r="F64" s="28"/>
+      <c r="G64" s="28"/>
+      <c r="L64" s="28"/>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A65" s="47"/>
+      <c r="C65" s="48"/>
+      <c r="E65" s="28"/>
+      <c r="F65" s="28"/>
+      <c r="G65" s="28"/>
+      <c r="L65" s="28"/>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A66" s="47"/>
+      <c r="C66" s="48"/>
+      <c r="E66" s="28"/>
+      <c r="F66" s="28"/>
+      <c r="G66" s="28"/>
+      <c r="L66" s="28"/>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A67" s="47"/>
+      <c r="C67" s="48"/>
+      <c r="E67" s="28"/>
+      <c r="F67" s="28"/>
+      <c r="G67" s="28"/>
+      <c r="L67" s="28"/>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A68" s="83" t="s">
+        <v>85</v>
+      </c>
+      <c r="B68" s="80" t="s">
+        <v>13</v>
+      </c>
+      <c r="C68" s="84" t="s">
+        <v>18</v>
+      </c>
+      <c r="D68" s="80" t="s">
+        <v>50</v>
+      </c>
+      <c r="E68" s="82">
+        <v>1000</v>
+      </c>
+      <c r="F68" s="28"/>
+      <c r="G68" s="28"/>
+      <c r="L68" s="28"/>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A69" s="44" t="s">
         <v>99</v>
       </c>
-      <c r="B63" s="46" t="s">
+      <c r="B69" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="C63" s="47" t="s">
+      <c r="C69" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="E63" s="53">
+      <c r="E69" s="52">
         <v>0</v>
       </c>
-      <c r="F63" s="53"/>
-      <c r="G63" s="53"/>
-      <c r="L63" s="53"/>
-    </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A64" s="48" t="s">
+      <c r="F69" s="52"/>
+      <c r="G69" s="52"/>
+      <c r="L69" s="52"/>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A70" s="47" t="s">
         <v>98</v>
       </c>
-      <c r="B64" s="29" t="s">
+      <c r="B70" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="C64" s="49" t="s">
+      <c r="C70" s="48" t="s">
         <v>19</v>
       </c>
-      <c r="E64" s="53">
+      <c r="E70" s="52">
         <v>1</v>
       </c>
-      <c r="F64" s="53"/>
-      <c r="G64" s="53"/>
-      <c r="L64" s="53"/>
-    </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A65" s="48" t="s">
+      <c r="F70" s="52"/>
+      <c r="G70" s="52"/>
+      <c r="L70" s="52"/>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A71" s="97" t="s">
         <v>96</v>
       </c>
-      <c r="B65" s="29" t="s">
+      <c r="B71" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="C65" s="49" t="s">
+      <c r="C71" s="98" t="s">
         <v>19</v>
       </c>
-      <c r="D65" s="29" t="s">
+      <c r="D71" s="42" t="s">
         <v>115</v>
       </c>
-      <c r="E65" s="53">
+      <c r="E71" s="99">
         <v>2</v>
       </c>
-      <c r="F65" s="53"/>
-      <c r="G65" s="53"/>
-      <c r="L65" s="53"/>
-    </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A66" s="48" t="s">
+      <c r="F71" s="52"/>
+      <c r="G71" s="52"/>
+      <c r="L71" s="52"/>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A72" s="47" t="s">
         <v>56</v>
-      </c>
-      <c r="B66" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="C66" s="49" t="s">
-        <v>19</v>
-      </c>
-      <c r="E66" s="53">
-        <v>3</v>
-      </c>
-      <c r="F66" s="53"/>
-      <c r="G66" s="53"/>
-      <c r="H66" s="53"/>
-      <c r="I66" s="53"/>
-      <c r="J66" s="53"/>
-      <c r="K66" s="53"/>
-      <c r="L66" s="53"/>
-    </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A67" s="48" t="s">
-        <v>116</v>
-      </c>
-      <c r="B67" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="C67" s="49" t="s">
-        <v>19</v>
-      </c>
-      <c r="E67" s="53">
-        <v>4</v>
-      </c>
-      <c r="F67" s="53"/>
-      <c r="G67" s="53"/>
-      <c r="H67" s="53"/>
-      <c r="I67" s="53"/>
-      <c r="J67" s="53"/>
-      <c r="K67" s="53"/>
-      <c r="L67" s="53"/>
-    </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A68" s="87" t="s">
-        <v>106</v>
-      </c>
-      <c r="B68" s="84" t="s">
-        <v>16</v>
-      </c>
-      <c r="C68" s="88" t="s">
-        <v>19</v>
-      </c>
-      <c r="D68" s="84" t="s">
-        <v>50</v>
-      </c>
-      <c r="E68" s="89">
-        <v>5</v>
-      </c>
-      <c r="F68" s="53"/>
-      <c r="G68" s="53"/>
-      <c r="H68" s="53"/>
-      <c r="I68" s="53"/>
-      <c r="J68" s="53"/>
-      <c r="K68" s="53"/>
-      <c r="L68" s="53"/>
-    </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A69" s="48" t="s">
-        <v>97</v>
-      </c>
-      <c r="B69" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="C69" s="49" t="s">
-        <v>19</v>
-      </c>
-      <c r="D69" s="29" t="s">
-        <v>115</v>
-      </c>
-      <c r="E69" s="53">
-        <v>6</v>
-      </c>
-      <c r="F69" s="53"/>
-      <c r="G69" s="53"/>
-      <c r="H69" s="53"/>
-      <c r="I69" s="53"/>
-      <c r="J69" s="53"/>
-      <c r="K69" s="53"/>
-      <c r="L69" s="53"/>
-    </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A70" s="50" t="s">
-        <v>119</v>
-      </c>
-      <c r="B70" s="51" t="s">
-        <v>16</v>
-      </c>
-      <c r="C70" s="52" t="s">
-        <v>19</v>
-      </c>
-      <c r="D70" s="29" t="s">
-        <v>115</v>
-      </c>
-      <c r="E70" s="53">
-        <v>7</v>
-      </c>
-      <c r="F70" s="53"/>
-      <c r="G70" s="53"/>
-      <c r="H70" s="53"/>
-      <c r="I70" s="53"/>
-      <c r="J70" s="53"/>
-      <c r="K70" s="53"/>
-      <c r="L70" s="53"/>
-    </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A71" s="48" t="s">
-        <v>152</v>
-      </c>
-      <c r="B71" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="C71" s="49" t="s">
-        <v>19</v>
-      </c>
-      <c r="D71" s="29" t="s">
-        <v>115</v>
-      </c>
-      <c r="E71" s="53">
-        <v>8</v>
-      </c>
-      <c r="F71" s="53"/>
-      <c r="G71" s="53"/>
-      <c r="H71" s="53"/>
-      <c r="I71" s="53"/>
-      <c r="J71" s="53"/>
-      <c r="K71" s="53"/>
-      <c r="L71" s="53"/>
-    </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A72" s="48" t="s">
-        <v>154</v>
       </c>
       <c r="B72" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="C72" s="49" t="s">
+      <c r="C72" s="48" t="s">
         <v>19</v>
       </c>
-      <c r="D72" s="29" t="s">
+      <c r="E72" s="52">
+        <v>3</v>
+      </c>
+      <c r="F72" s="52"/>
+      <c r="G72" s="52"/>
+      <c r="H72" s="52"/>
+      <c r="I72" s="52"/>
+      <c r="J72" s="52"/>
+      <c r="K72" s="52"/>
+      <c r="L72" s="52"/>
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A73" s="47" t="s">
+        <v>116</v>
+      </c>
+      <c r="B73" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="C73" s="48" t="s">
+        <v>19</v>
+      </c>
+      <c r="E73" s="52">
+        <v>4</v>
+      </c>
+      <c r="F73" s="52"/>
+      <c r="G73" s="52"/>
+      <c r="H73" s="52"/>
+      <c r="I73" s="52"/>
+      <c r="J73" s="52"/>
+      <c r="K73" s="52"/>
+      <c r="L73" s="52"/>
+    </row>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A74" s="83" t="s">
+        <v>106</v>
+      </c>
+      <c r="B74" s="80" t="s">
+        <v>16</v>
+      </c>
+      <c r="C74" s="84" t="s">
+        <v>19</v>
+      </c>
+      <c r="D74" s="80" t="s">
+        <v>50</v>
+      </c>
+      <c r="E74" s="85">
+        <v>5</v>
+      </c>
+      <c r="F74" s="52"/>
+      <c r="G74" s="52"/>
+      <c r="H74" s="52"/>
+      <c r="I74" s="52"/>
+      <c r="J74" s="52"/>
+      <c r="K74" s="52"/>
+      <c r="L74" s="52"/>
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A75" s="97" t="s">
+        <v>97</v>
+      </c>
+      <c r="B75" s="42" t="s">
+        <v>16</v>
+      </c>
+      <c r="C75" s="98" t="s">
+        <v>19</v>
+      </c>
+      <c r="D75" s="42" t="s">
         <v>115</v>
       </c>
-      <c r="E72" s="53">
+      <c r="E75" s="99">
+        <v>6</v>
+      </c>
+      <c r="F75" s="52"/>
+      <c r="G75" s="52"/>
+      <c r="H75" s="52"/>
+      <c r="I75" s="52"/>
+      <c r="J75" s="52"/>
+      <c r="K75" s="52"/>
+      <c r="L75" s="52"/>
+    </row>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A76" s="100" t="s">
+        <v>119</v>
+      </c>
+      <c r="B76" s="101" t="s">
+        <v>16</v>
+      </c>
+      <c r="C76" s="102" t="s">
+        <v>19</v>
+      </c>
+      <c r="D76" s="42" t="s">
+        <v>115</v>
+      </c>
+      <c r="E76" s="99">
+        <v>7</v>
+      </c>
+      <c r="F76" s="52"/>
+      <c r="G76" s="52"/>
+      <c r="H76" s="52"/>
+      <c r="I76" s="52"/>
+      <c r="J76" s="52"/>
+      <c r="K76" s="52"/>
+      <c r="L76" s="52"/>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A77" s="97" t="s">
+        <v>152</v>
+      </c>
+      <c r="B77" s="42" t="s">
+        <v>16</v>
+      </c>
+      <c r="C77" s="98" t="s">
+        <v>19</v>
+      </c>
+      <c r="D77" s="42" t="s">
+        <v>115</v>
+      </c>
+      <c r="E77" s="99">
+        <v>8</v>
+      </c>
+      <c r="F77" s="52"/>
+      <c r="G77" s="52"/>
+      <c r="H77" s="52"/>
+      <c r="I77" s="52"/>
+      <c r="J77" s="52"/>
+      <c r="K77" s="52"/>
+      <c r="L77" s="52"/>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A78" s="97" t="s">
+        <v>154</v>
+      </c>
+      <c r="B78" s="42" t="s">
+        <v>16</v>
+      </c>
+      <c r="C78" s="98" t="s">
+        <v>19</v>
+      </c>
+      <c r="D78" s="42" t="s">
+        <v>115</v>
+      </c>
+      <c r="E78" s="99">
         <v>9</v>
       </c>
-      <c r="F72" s="53"/>
-      <c r="G72" s="53"/>
-      <c r="H72" s="53"/>
-      <c r="I72" s="53"/>
-      <c r="J72" s="53"/>
-      <c r="K72" s="53"/>
-      <c r="L72" s="53"/>
-    </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A73" s="87" t="s">
+      <c r="F78" s="52"/>
+      <c r="G78" s="52"/>
+      <c r="H78" s="52"/>
+      <c r="I78" s="52"/>
+      <c r="J78" s="52"/>
+      <c r="K78" s="52"/>
+      <c r="L78" s="52"/>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A79" s="83" t="s">
         <v>155</v>
       </c>
-      <c r="B73" s="84" t="s">
+      <c r="B79" s="80" t="s">
         <v>16</v>
       </c>
-      <c r="C73" s="88" t="s">
+      <c r="C79" s="84" t="s">
         <v>19</v>
       </c>
-      <c r="D73" s="84" t="s">
+      <c r="D79" s="80" t="s">
         <v>50</v>
       </c>
-      <c r="E73" s="89">
+      <c r="E79" s="85">
         <v>10</v>
       </c>
-      <c r="F73" s="53"/>
-      <c r="G73" s="53"/>
-      <c r="H73" s="53"/>
-      <c r="I73" s="53"/>
-      <c r="J73" s="53"/>
-      <c r="K73" s="53"/>
-      <c r="L73" s="53"/>
-    </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A74" s="87" t="s">
+      <c r="F79" s="52"/>
+      <c r="G79" s="52"/>
+      <c r="H79" s="52"/>
+      <c r="I79" s="52"/>
+      <c r="J79" s="52"/>
+      <c r="K79" s="52"/>
+      <c r="L79" s="52"/>
+    </row>
+    <row r="80" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A80" s="83" t="s">
         <v>167</v>
       </c>
-      <c r="B74" s="84" t="s">
+      <c r="B80" s="80" t="s">
         <v>16</v>
       </c>
-      <c r="C74" s="88" t="s">
+      <c r="C80" s="84" t="s">
         <v>19</v>
       </c>
-      <c r="D74" s="84"/>
-      <c r="E74" s="89">
+      <c r="D80" s="80"/>
+      <c r="E80" s="85">
         <v>20</v>
       </c>
-      <c r="F74" s="53"/>
-      <c r="G74" s="53"/>
-      <c r="H74" s="53"/>
-      <c r="I74" s="53"/>
-      <c r="J74" s="53"/>
-      <c r="K74" s="53"/>
-      <c r="L74" s="53"/>
-    </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A75" s="87" t="s">
+      <c r="F80" s="52"/>
+      <c r="G80" s="52"/>
+      <c r="H80" s="52"/>
+      <c r="I80" s="52"/>
+      <c r="J80" s="52"/>
+      <c r="K80" s="52"/>
+      <c r="L80" s="52"/>
+    </row>
+    <row r="81" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A81" s="83" t="s">
         <v>168</v>
       </c>
-      <c r="B75" s="84" t="s">
+      <c r="B81" s="80" t="s">
         <v>16</v>
       </c>
-      <c r="C75" s="88" t="s">
+      <c r="C81" s="84" t="s">
         <v>19</v>
       </c>
-      <c r="D75" s="84"/>
-      <c r="E75" s="89">
+      <c r="D81" s="80"/>
+      <c r="E81" s="85">
         <v>20.010000000000002</v>
       </c>
-      <c r="F75" s="53"/>
-      <c r="G75" s="53"/>
-      <c r="H75" s="53"/>
-      <c r="I75" s="53"/>
-      <c r="J75" s="53"/>
-      <c r="K75" s="53"/>
-      <c r="L75" s="53"/>
-    </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A76" s="87" t="s">
+      <c r="F81" s="52"/>
+      <c r="G81" s="52"/>
+      <c r="H81" s="52"/>
+      <c r="I81" s="52"/>
+      <c r="J81" s="52"/>
+      <c r="K81" s="52"/>
+      <c r="L81" s="52"/>
+    </row>
+    <row r="82" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A82" s="83" t="s">
         <v>169</v>
       </c>
-      <c r="B76" s="84" t="s">
+      <c r="B82" s="80" t="s">
         <v>16</v>
       </c>
-      <c r="C76" s="88" t="s">
+      <c r="C82" s="84" t="s">
         <v>19</v>
       </c>
-      <c r="D76" s="84"/>
-      <c r="E76" s="89">
+      <c r="D82" s="80"/>
+      <c r="E82" s="85">
         <v>20.02</v>
       </c>
-      <c r="F76" s="53"/>
-      <c r="G76" s="53"/>
-      <c r="H76" s="53"/>
-      <c r="I76" s="53"/>
-      <c r="J76" s="53"/>
-      <c r="K76" s="53"/>
-      <c r="L76" s="53"/>
-    </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A77" s="87" t="s">
+      <c r="F82" s="52"/>
+      <c r="G82" s="52"/>
+      <c r="H82" s="52"/>
+      <c r="I82" s="52"/>
+      <c r="J82" s="52"/>
+      <c r="K82" s="52"/>
+      <c r="L82" s="52"/>
+    </row>
+    <row r="83" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A83" s="83" t="s">
         <v>170</v>
       </c>
-      <c r="B77" s="84" t="s">
+      <c r="B83" s="80" t="s">
         <v>16</v>
       </c>
-      <c r="C77" s="88" t="s">
+      <c r="C83" s="84" t="s">
         <v>19</v>
       </c>
-      <c r="D77" s="84"/>
-      <c r="E77" s="89">
+      <c r="D83" s="80"/>
+      <c r="E83" s="85">
         <v>20.03</v>
       </c>
-      <c r="F77" s="53"/>
-      <c r="G77" s="53"/>
-      <c r="H77" s="53"/>
-      <c r="I77" s="53"/>
-      <c r="J77" s="53"/>
-      <c r="K77" s="53"/>
-      <c r="L77" s="53"/>
-    </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A78" s="87" t="s">
+      <c r="F83" s="52"/>
+      <c r="G83" s="52"/>
+      <c r="H83" s="52"/>
+      <c r="I83" s="52"/>
+      <c r="J83" s="52"/>
+      <c r="K83" s="52"/>
+      <c r="L83" s="52"/>
+    </row>
+    <row r="84" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A84" s="83" t="s">
         <v>194</v>
       </c>
-      <c r="B78" s="84" t="s">
+      <c r="B84" s="80" t="s">
         <v>16</v>
       </c>
-      <c r="C78" s="88" t="s">
+      <c r="C84" s="84" t="s">
         <v>19</v>
       </c>
-      <c r="D78" s="84"/>
-      <c r="E78" s="89">
+      <c r="D84" s="80"/>
+      <c r="E84" s="85">
         <v>20.05</v>
       </c>
-      <c r="F78" s="53"/>
-      <c r="G78" s="53"/>
-      <c r="H78" s="53"/>
-      <c r="I78" s="53"/>
-      <c r="J78" s="53"/>
-      <c r="K78" s="53"/>
-      <c r="L78" s="53"/>
-    </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A79" s="87" t="s">
+      <c r="F84" s="52"/>
+      <c r="G84" s="52"/>
+      <c r="H84" s="52"/>
+      <c r="I84" s="52"/>
+      <c r="J84" s="52"/>
+      <c r="K84" s="52"/>
+      <c r="L84" s="52"/>
+    </row>
+    <row r="85" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A85" s="83" t="s">
         <v>195</v>
       </c>
-      <c r="B79" s="84" t="s">
+      <c r="B85" s="80" t="s">
         <v>16</v>
       </c>
-      <c r="C79" s="88" t="s">
+      <c r="C85" s="84" t="s">
         <v>19</v>
       </c>
-      <c r="D79" s="84"/>
-      <c r="E79" s="89">
+      <c r="D85" s="80"/>
+      <c r="E85" s="85">
         <v>20.059999999999999</v>
       </c>
-      <c r="F79" s="53"/>
-      <c r="G79" s="53"/>
-      <c r="H79" s="53"/>
-      <c r="I79" s="53"/>
-      <c r="J79" s="53"/>
-      <c r="K79" s="53"/>
-      <c r="L79" s="53"/>
-    </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A80" s="48" t="s">
+      <c r="F85" s="52"/>
+      <c r="G85" s="52"/>
+      <c r="H85" s="52"/>
+      <c r="I85" s="52"/>
+      <c r="J85" s="52"/>
+      <c r="K85" s="52"/>
+      <c r="L85" s="52"/>
+    </row>
+    <row r="86" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A86" s="97" t="s">
         <v>173</v>
       </c>
-      <c r="B80" s="29" t="s">
+      <c r="B86" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="C80" s="49" t="s">
+      <c r="C86" s="98" t="s">
         <v>19</v>
       </c>
-      <c r="D80" s="29" t="s">
+      <c r="D86" s="42" t="s">
         <v>115</v>
       </c>
-      <c r="E80" s="53">
+      <c r="E86" s="99">
         <v>30</v>
       </c>
-      <c r="F80" s="53"/>
-      <c r="G80" s="53"/>
-      <c r="H80" s="53"/>
-      <c r="I80" s="53"/>
-      <c r="J80" s="53"/>
-      <c r="K80" s="53"/>
-      <c r="L80" s="53"/>
-    </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A81" s="48"/>
-      <c r="C81" s="49"/>
-      <c r="E81" s="53"/>
-      <c r="F81" s="53"/>
-      <c r="G81" s="53"/>
-      <c r="H81" s="53"/>
-      <c r="I81" s="53"/>
-      <c r="J81" s="53"/>
-      <c r="K81" s="53"/>
-      <c r="L81" s="53"/>
-    </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A82" s="48"/>
-      <c r="C82" s="49"/>
-      <c r="E82" s="53"/>
-      <c r="F82" s="53"/>
-      <c r="G82" s="53"/>
-      <c r="H82" s="53"/>
-      <c r="I82" s="53"/>
-      <c r="J82" s="53"/>
-      <c r="K82" s="53"/>
-      <c r="L82" s="53"/>
-    </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A83" s="48"/>
-      <c r="C83" s="49"/>
-      <c r="E83" s="53"/>
-      <c r="F83" s="53"/>
-      <c r="G83" s="53"/>
-      <c r="H83" s="53"/>
-      <c r="I83" s="53"/>
-      <c r="J83" s="53"/>
-      <c r="K83" s="53"/>
-      <c r="L83" s="53"/>
-    </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A84" s="48"/>
-      <c r="C84" s="49"/>
-      <c r="E84" s="53"/>
-      <c r="F84" s="53"/>
-      <c r="G84" s="53"/>
-      <c r="H84" s="53"/>
-      <c r="I84" s="53"/>
-      <c r="J84" s="53"/>
-      <c r="K84" s="53"/>
-      <c r="L84" s="53"/>
-    </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A85" s="48"/>
-      <c r="C85" s="49"/>
-      <c r="E85" s="53"/>
-      <c r="F85" s="53"/>
-      <c r="G85" s="53"/>
-      <c r="H85" s="53"/>
-      <c r="I85" s="53"/>
-      <c r="J85" s="53"/>
-      <c r="K85" s="53"/>
-      <c r="L85" s="53"/>
-    </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A86" s="48"/>
-      <c r="C86" s="49"/>
-      <c r="E86" s="53"/>
-      <c r="F86" s="53"/>
-      <c r="G86" s="53"/>
-      <c r="H86" s="53"/>
-      <c r="I86" s="53"/>
-      <c r="J86" s="53"/>
-      <c r="K86" s="53"/>
-      <c r="L86" s="53"/>
+      <c r="F86" s="52"/>
+      <c r="G86" s="52"/>
+      <c r="H86" s="52"/>
+      <c r="I86" s="52"/>
+      <c r="J86" s="52"/>
+      <c r="K86" s="52"/>
+      <c r="L86" s="52"/>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A87" s="45" t="s">
+      <c r="A87" s="47"/>
+      <c r="C87" s="48"/>
+      <c r="E87" s="52"/>
+      <c r="F87" s="52"/>
+      <c r="G87" s="52"/>
+      <c r="H87" s="52"/>
+      <c r="I87" s="52"/>
+      <c r="J87" s="52"/>
+      <c r="K87" s="52"/>
+      <c r="L87" s="52"/>
+    </row>
+    <row r="88" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A88" s="47"/>
+      <c r="C88" s="48"/>
+      <c r="E88" s="52"/>
+      <c r="F88" s="52"/>
+      <c r="G88" s="52"/>
+      <c r="H88" s="52"/>
+      <c r="I88" s="52"/>
+      <c r="J88" s="52"/>
+      <c r="K88" s="52"/>
+      <c r="L88" s="52"/>
+    </row>
+    <row r="89" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A89" s="47"/>
+      <c r="C89" s="48"/>
+      <c r="E89" s="52"/>
+      <c r="F89" s="52"/>
+      <c r="G89" s="52"/>
+      <c r="H89" s="52"/>
+      <c r="I89" s="52"/>
+      <c r="J89" s="52"/>
+      <c r="K89" s="52"/>
+      <c r="L89" s="52"/>
+    </row>
+    <row r="90" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A90" s="47"/>
+      <c r="C90" s="48"/>
+      <c r="E90" s="52"/>
+      <c r="F90" s="52"/>
+      <c r="G90" s="52"/>
+      <c r="H90" s="52"/>
+      <c r="I90" s="52"/>
+      <c r="J90" s="52"/>
+      <c r="K90" s="52"/>
+      <c r="L90" s="52"/>
+    </row>
+    <row r="91" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A91" s="47"/>
+      <c r="C91" s="48"/>
+      <c r="E91" s="52"/>
+      <c r="F91" s="52"/>
+      <c r="G91" s="52"/>
+      <c r="H91" s="52"/>
+      <c r="I91" s="52"/>
+      <c r="J91" s="52"/>
+      <c r="K91" s="52"/>
+      <c r="L91" s="52"/>
+    </row>
+    <row r="92" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A92" s="47"/>
+      <c r="C92" s="48"/>
+      <c r="E92" s="52"/>
+      <c r="F92" s="52"/>
+      <c r="G92" s="52"/>
+      <c r="H92" s="52"/>
+      <c r="I92" s="52"/>
+      <c r="J92" s="52"/>
+      <c r="K92" s="52"/>
+      <c r="L92" s="52"/>
+    </row>
+    <row r="93" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A93" s="44" t="s">
         <v>93</v>
       </c>
-      <c r="B87" s="46" t="s">
+      <c r="B93" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="C87" s="47" t="s">
+      <c r="C93" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="E87" s="53">
+      <c r="E93" s="52">
         <v>60</v>
       </c>
-      <c r="F87" s="53"/>
-      <c r="G87" s="53"/>
-      <c r="H87" s="53"/>
-      <c r="I87" s="53"/>
-      <c r="J87" s="53"/>
-      <c r="K87" s="53"/>
-      <c r="L87" s="53"/>
-    </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A88" s="48" t="s">
+      <c r="F93" s="52"/>
+      <c r="G93" s="52"/>
+      <c r="H93" s="52"/>
+      <c r="I93" s="52"/>
+      <c r="J93" s="52"/>
+      <c r="K93" s="52"/>
+      <c r="L93" s="52"/>
+    </row>
+    <row r="94" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A94" s="47" t="s">
         <v>58</v>
       </c>
-      <c r="B88" s="29" t="s">
+      <c r="B94" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="C88" s="49" t="s">
+      <c r="C94" s="48" t="s">
         <v>19</v>
       </c>
-      <c r="E88" s="53">
+      <c r="E94" s="52">
         <v>61</v>
       </c>
-      <c r="F88" s="53"/>
-      <c r="G88" s="53"/>
-      <c r="H88" s="53"/>
-      <c r="I88" s="53"/>
-      <c r="J88" s="53"/>
-      <c r="K88" s="53"/>
-      <c r="L88" s="53"/>
-    </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A89" s="48" t="s">
+      <c r="F94" s="52"/>
+      <c r="G94" s="52"/>
+      <c r="H94" s="52"/>
+      <c r="I94" s="52"/>
+      <c r="J94" s="52"/>
+      <c r="K94" s="52"/>
+      <c r="L94" s="52"/>
+    </row>
+    <row r="95" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A95" s="47" t="s">
         <v>59</v>
       </c>
-      <c r="B89" s="29" t="s">
+      <c r="B95" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="C89" s="49" t="s">
+      <c r="C95" s="48" t="s">
         <v>19</v>
       </c>
-      <c r="E89" s="53">
+      <c r="E95" s="52">
         <v>62</v>
       </c>
-      <c r="F89" s="53"/>
-      <c r="G89" s="53"/>
-      <c r="H89" s="53"/>
-      <c r="I89" s="53"/>
-      <c r="J89" s="53"/>
-      <c r="K89" s="53"/>
-      <c r="L89" s="53"/>
-    </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A90" s="48" t="s">
+      <c r="F95" s="52"/>
+      <c r="G95" s="52"/>
+      <c r="H95" s="52"/>
+      <c r="I95" s="52"/>
+      <c r="J95" s="52"/>
+      <c r="K95" s="52"/>
+      <c r="L95" s="52"/>
+    </row>
+    <row r="96" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A96" s="47" t="s">
         <v>94</v>
       </c>
-      <c r="B90" s="29" t="s">
+      <c r="B96" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="C90" s="49" t="s">
+      <c r="C96" s="48" t="s">
         <v>19</v>
       </c>
-      <c r="E90" s="53">
+      <c r="E96" s="52">
         <v>63</v>
       </c>
-      <c r="F90" s="53"/>
-      <c r="G90" s="53"/>
-      <c r="H90" s="53"/>
-      <c r="I90" s="53"/>
-      <c r="J90" s="53"/>
-      <c r="K90" s="53"/>
-      <c r="L90" s="53"/>
-    </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A91" s="48" t="s">
+      <c r="F96" s="52"/>
+      <c r="G96" s="52"/>
+      <c r="H96" s="52"/>
+      <c r="I96" s="52"/>
+      <c r="J96" s="52"/>
+      <c r="K96" s="52"/>
+      <c r="L96" s="52"/>
+    </row>
+    <row r="97" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A97" s="47" t="s">
         <v>60</v>
       </c>
-      <c r="B91" s="29" t="s">
+      <c r="B97" s="29" t="s">
         <v>95</v>
       </c>
-      <c r="C91" s="49" t="s">
+      <c r="C97" s="48" t="s">
         <v>19</v>
       </c>
-      <c r="E91" s="53">
+      <c r="E97" s="52">
         <v>63.01</v>
       </c>
-      <c r="F91" s="53"/>
-      <c r="G91" s="53"/>
-      <c r="H91" s="53"/>
-      <c r="I91" s="53"/>
-      <c r="J91" s="53"/>
-      <c r="K91" s="53"/>
-      <c r="L91" s="53"/>
-    </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A92" s="48" t="s">
+      <c r="F97" s="52"/>
+      <c r="G97" s="52"/>
+      <c r="H97" s="52"/>
+      <c r="I97" s="52"/>
+      <c r="J97" s="52"/>
+      <c r="K97" s="52"/>
+      <c r="L97" s="52"/>
+    </row>
+    <row r="98" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A98" s="47" t="s">
         <v>61</v>
-      </c>
-      <c r="B92" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="C92" s="49" t="s">
-        <v>19</v>
-      </c>
-      <c r="E92" s="53">
-        <v>64</v>
-      </c>
-      <c r="F92" s="53"/>
-      <c r="G92" s="53"/>
-      <c r="H92" s="53"/>
-      <c r="I92" s="53"/>
-      <c r="J92" s="53"/>
-      <c r="K92" s="53"/>
-      <c r="L92" s="53"/>
-    </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A93" s="50" t="s">
-        <v>92</v>
-      </c>
-      <c r="B93" s="51" t="s">
-        <v>16</v>
-      </c>
-      <c r="C93" s="52" t="s">
-        <v>19</v>
-      </c>
-      <c r="E93" s="53">
-        <v>65</v>
-      </c>
-      <c r="F93" s="53"/>
-      <c r="G93" s="53"/>
-      <c r="H93" s="53"/>
-      <c r="I93" s="53"/>
-      <c r="J93" s="53"/>
-      <c r="K93" s="53"/>
-      <c r="L93" s="53"/>
-    </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="C94" s="49"/>
-      <c r="E94" s="53"/>
-      <c r="F94" s="53"/>
-      <c r="G94" s="53"/>
-      <c r="H94" s="53"/>
-      <c r="I94" s="53"/>
-      <c r="J94" s="53"/>
-      <c r="K94" s="53"/>
-      <c r="L94" s="53"/>
-    </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A95" s="48"/>
-      <c r="C95" s="49"/>
-      <c r="E95" s="53"/>
-      <c r="F95" s="53"/>
-      <c r="G95" s="53"/>
-      <c r="H95" s="53"/>
-      <c r="I95" s="53"/>
-      <c r="J95" s="53"/>
-      <c r="K95" s="53"/>
-      <c r="L95" s="53"/>
-    </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A96" s="50"/>
-      <c r="B96" s="51"/>
-      <c r="C96" s="52"/>
-      <c r="E96" s="53"/>
-      <c r="F96" s="53"/>
-      <c r="G96" s="53"/>
-      <c r="H96" s="53"/>
-      <c r="I96" s="53"/>
-      <c r="J96" s="53"/>
-      <c r="K96" s="53"/>
-      <c r="L96" s="53"/>
-    </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A97" s="45" t="s">
-        <v>86</v>
-      </c>
-      <c r="B97" s="46" t="s">
-        <v>16</v>
-      </c>
-      <c r="C97" s="47" t="s">
-        <v>19</v>
-      </c>
-      <c r="E97" s="53">
-        <v>70</v>
-      </c>
-      <c r="F97" s="53"/>
-      <c r="G97" s="53"/>
-      <c r="H97" s="53"/>
-      <c r="I97" s="53"/>
-      <c r="J97" s="53"/>
-      <c r="K97" s="53"/>
-      <c r="L97" s="53"/>
-    </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A98" s="48" t="s">
-        <v>87</v>
       </c>
       <c r="B98" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="C98" s="49" t="s">
+      <c r="C98" s="48" t="s">
         <v>19</v>
       </c>
-      <c r="E98" s="53">
+      <c r="E98" s="52">
+        <v>64</v>
+      </c>
+      <c r="F98" s="52"/>
+      <c r="G98" s="52"/>
+      <c r="H98" s="52"/>
+      <c r="I98" s="52"/>
+      <c r="J98" s="52"/>
+      <c r="K98" s="52"/>
+      <c r="L98" s="52"/>
+    </row>
+    <row r="99" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A99" s="49" t="s">
+        <v>92</v>
+      </c>
+      <c r="B99" s="50" t="s">
+        <v>16</v>
+      </c>
+      <c r="C99" s="51" t="s">
+        <v>19</v>
+      </c>
+      <c r="E99" s="52">
+        <v>65</v>
+      </c>
+      <c r="F99" s="52"/>
+      <c r="G99" s="52"/>
+      <c r="H99" s="52"/>
+      <c r="I99" s="52"/>
+      <c r="J99" s="52"/>
+      <c r="K99" s="52"/>
+      <c r="L99" s="52"/>
+    </row>
+    <row r="100" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="C100" s="48"/>
+      <c r="E100" s="52"/>
+      <c r="F100" s="52"/>
+      <c r="G100" s="52"/>
+      <c r="H100" s="52"/>
+      <c r="I100" s="52"/>
+      <c r="J100" s="52"/>
+      <c r="K100" s="52"/>
+      <c r="L100" s="52"/>
+    </row>
+    <row r="101" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A101" s="47"/>
+      <c r="C101" s="48"/>
+      <c r="E101" s="52"/>
+      <c r="F101" s="52"/>
+      <c r="G101" s="52"/>
+      <c r="H101" s="52"/>
+      <c r="I101" s="52"/>
+      <c r="J101" s="52"/>
+      <c r="K101" s="52"/>
+      <c r="L101" s="52"/>
+    </row>
+    <row r="102" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A102" s="49"/>
+      <c r="B102" s="50"/>
+      <c r="C102" s="51"/>
+      <c r="E102" s="52"/>
+      <c r="F102" s="52"/>
+      <c r="G102" s="52"/>
+      <c r="H102" s="52"/>
+      <c r="I102" s="52"/>
+      <c r="J102" s="52"/>
+      <c r="K102" s="52"/>
+      <c r="L102" s="52"/>
+    </row>
+    <row r="103" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A103" s="44" t="s">
+        <v>86</v>
+      </c>
+      <c r="B103" s="45" t="s">
+        <v>16</v>
+      </c>
+      <c r="C103" s="46" t="s">
+        <v>19</v>
+      </c>
+      <c r="E103" s="52">
+        <v>70</v>
+      </c>
+      <c r="F103" s="52"/>
+      <c r="G103" s="52"/>
+      <c r="H103" s="52"/>
+      <c r="I103" s="52"/>
+      <c r="J103" s="52"/>
+      <c r="K103" s="52"/>
+      <c r="L103" s="52"/>
+    </row>
+    <row r="104" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A104" s="47" t="s">
+        <v>87</v>
+      </c>
+      <c r="B104" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="C104" s="48" t="s">
+        <v>19</v>
+      </c>
+      <c r="E104" s="52">
         <v>71</v>
       </c>
-      <c r="F98" s="53"/>
-      <c r="G98" s="53"/>
-      <c r="H98" s="53"/>
-      <c r="I98" s="53"/>
-      <c r="J98" s="53"/>
-      <c r="K98" s="53"/>
-      <c r="L98" s="53"/>
-    </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A99" s="48" t="s">
+      <c r="F104" s="52"/>
+      <c r="G104" s="52"/>
+      <c r="H104" s="52"/>
+      <c r="I104" s="52"/>
+      <c r="J104" s="52"/>
+      <c r="K104" s="52"/>
+      <c r="L104" s="52"/>
+    </row>
+    <row r="105" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A105" s="47" t="s">
         <v>88</v>
       </c>
-      <c r="B99" s="29" t="s">
+      <c r="B105" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="C99" s="49" t="s">
+      <c r="C105" s="48" t="s">
         <v>19</v>
       </c>
-      <c r="E99" s="53">
+      <c r="E105" s="52">
         <v>72</v>
       </c>
-      <c r="F99" s="53"/>
-      <c r="G99" s="53"/>
-      <c r="H99" s="53"/>
-      <c r="I99" s="53"/>
-      <c r="J99" s="53"/>
-      <c r="K99" s="53"/>
-      <c r="L99" s="53"/>
-    </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A100" s="48" t="s">
+      <c r="F105" s="52"/>
+      <c r="G105" s="52"/>
+      <c r="H105" s="52"/>
+      <c r="I105" s="52"/>
+      <c r="J105" s="52"/>
+      <c r="K105" s="52"/>
+      <c r="L105" s="52"/>
+    </row>
+    <row r="106" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A106" s="47" t="s">
         <v>89</v>
       </c>
-      <c r="B100" s="29" t="s">
+      <c r="B106" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="C100" s="49" t="s">
+      <c r="C106" s="48" t="s">
         <v>19</v>
       </c>
-      <c r="E100" s="53">
+      <c r="E106" s="52">
         <v>73</v>
       </c>
-      <c r="F100" s="53"/>
-      <c r="G100" s="53"/>
-      <c r="H100" s="53"/>
-      <c r="I100" s="53"/>
-      <c r="J100" s="53"/>
-      <c r="K100" s="53"/>
-      <c r="L100" s="53"/>
-    </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A101" s="48" t="s">
+      <c r="F106" s="52"/>
+      <c r="G106" s="52"/>
+      <c r="H106" s="52"/>
+      <c r="I106" s="52"/>
+      <c r="J106" s="52"/>
+      <c r="K106" s="52"/>
+      <c r="L106" s="52"/>
+    </row>
+    <row r="107" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A107" s="47" t="s">
         <v>90</v>
       </c>
-      <c r="B101" s="29" t="s">
+      <c r="B107" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="C101" s="49" t="s">
+      <c r="C107" s="48" t="s">
         <v>19</v>
       </c>
-      <c r="E101" s="53">
+      <c r="E107" s="52">
         <v>74</v>
       </c>
-      <c r="F101" s="53"/>
-      <c r="G101" s="53"/>
-      <c r="H101" s="53"/>
-      <c r="I101" s="53"/>
-      <c r="J101" s="53"/>
-      <c r="K101" s="53"/>
-      <c r="L101" s="53"/>
-    </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A102" s="48" t="s">
+      <c r="F107" s="52"/>
+      <c r="G107" s="52"/>
+      <c r="H107" s="52"/>
+      <c r="I107" s="52"/>
+      <c r="J107" s="52"/>
+      <c r="K107" s="52"/>
+      <c r="L107" s="52"/>
+    </row>
+    <row r="108" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A108" s="47" t="s">
         <v>91</v>
-      </c>
-      <c r="B102" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="C102" s="49" t="s">
-        <v>19</v>
-      </c>
-      <c r="E102" s="53">
-        <v>75</v>
-      </c>
-      <c r="F102" s="53"/>
-      <c r="G102" s="53"/>
-      <c r="H102" s="53"/>
-      <c r="I102" s="53"/>
-      <c r="J102" s="53"/>
-      <c r="K102" s="53"/>
-      <c r="L102" s="53"/>
-    </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A103" s="48" t="s">
-        <v>113</v>
-      </c>
-      <c r="B103" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="C103" s="49" t="s">
-        <v>19</v>
-      </c>
-      <c r="E103" s="53">
-        <v>76</v>
-      </c>
-      <c r="F103" s="53"/>
-      <c r="G103" s="53"/>
-      <c r="H103" s="53"/>
-      <c r="I103" s="53"/>
-      <c r="J103" s="53"/>
-      <c r="K103" s="53"/>
-      <c r="L103" s="53"/>
-    </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A104" s="50" t="s">
-        <v>114</v>
-      </c>
-      <c r="B104" s="51" t="s">
-        <v>95</v>
-      </c>
-      <c r="C104" s="52" t="s">
-        <v>19</v>
-      </c>
-      <c r="E104" s="53">
-        <v>77</v>
-      </c>
-      <c r="F104" s="53"/>
-      <c r="G104" s="53"/>
-      <c r="H104" s="53"/>
-      <c r="I104" s="53"/>
-      <c r="J104" s="53"/>
-      <c r="K104" s="53"/>
-      <c r="L104" s="53"/>
-    </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A105" s="48"/>
-      <c r="C105" s="49"/>
-      <c r="E105" s="53"/>
-      <c r="F105" s="53"/>
-      <c r="G105" s="53"/>
-      <c r="H105" s="53"/>
-      <c r="I105" s="53"/>
-      <c r="J105" s="53"/>
-      <c r="K105" s="53"/>
-      <c r="L105" s="53"/>
-    </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A106" s="50"/>
-      <c r="B106" s="51"/>
-      <c r="C106" s="52"/>
-      <c r="E106" s="53"/>
-      <c r="F106" s="53"/>
-      <c r="G106" s="53"/>
-      <c r="H106" s="53"/>
-      <c r="I106" s="53"/>
-      <c r="J106" s="53"/>
-      <c r="K106" s="53"/>
-      <c r="L106" s="53"/>
-    </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A107" s="45" t="s">
-        <v>53</v>
-      </c>
-      <c r="B107" s="46" t="s">
-        <v>16</v>
-      </c>
-      <c r="C107" s="47" t="s">
-        <v>51</v>
-      </c>
-      <c r="E107" s="53">
-        <v>0</v>
-      </c>
-      <c r="F107" s="53"/>
-      <c r="G107" s="53"/>
-      <c r="H107" s="53"/>
-      <c r="I107" s="53"/>
-      <c r="J107" s="53"/>
-      <c r="K107" s="53"/>
-      <c r="L107" s="53"/>
-    </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A108" s="48" t="s">
-        <v>54</v>
       </c>
       <c r="B108" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="C108" s="49" t="s">
-        <v>51</v>
-      </c>
-      <c r="E108" s="53">
-        <v>0.01</v>
-      </c>
-      <c r="F108" s="53"/>
-      <c r="G108" s="53"/>
-      <c r="H108" s="53"/>
-      <c r="I108" s="53"/>
-      <c r="J108" s="53"/>
-      <c r="K108" s="53"/>
-      <c r="L108" s="53"/>
+      <c r="C108" s="48" t="s">
+        <v>19</v>
+      </c>
+      <c r="E108" s="52">
+        <v>75</v>
+      </c>
+      <c r="F108" s="52"/>
+      <c r="G108" s="52"/>
+      <c r="H108" s="52"/>
+      <c r="I108" s="52"/>
+      <c r="J108" s="52"/>
+      <c r="K108" s="52"/>
+      <c r="L108" s="52"/>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A109" s="48" t="s">
-        <v>55</v>
+      <c r="A109" s="47" t="s">
+        <v>113</v>
       </c>
       <c r="B109" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="C109" s="49" t="s">
+      <c r="C109" s="48" t="s">
+        <v>19</v>
+      </c>
+      <c r="E109" s="52">
+        <v>76</v>
+      </c>
+      <c r="F109" s="52"/>
+      <c r="G109" s="52"/>
+      <c r="H109" s="52"/>
+      <c r="I109" s="52"/>
+      <c r="J109" s="52"/>
+      <c r="K109" s="52"/>
+      <c r="L109" s="52"/>
+    </row>
+    <row r="110" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A110" s="49" t="s">
+        <v>114</v>
+      </c>
+      <c r="B110" s="50" t="s">
+        <v>95</v>
+      </c>
+      <c r="C110" s="51" t="s">
+        <v>19</v>
+      </c>
+      <c r="E110" s="52">
+        <v>77</v>
+      </c>
+      <c r="F110" s="52"/>
+      <c r="G110" s="52"/>
+      <c r="H110" s="52"/>
+      <c r="I110" s="52"/>
+      <c r="J110" s="52"/>
+      <c r="K110" s="52"/>
+      <c r="L110" s="52"/>
+    </row>
+    <row r="111" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A111" s="47"/>
+      <c r="C111" s="48"/>
+      <c r="E111" s="52"/>
+      <c r="F111" s="52"/>
+      <c r="G111" s="52"/>
+      <c r="H111" s="52"/>
+      <c r="I111" s="52"/>
+      <c r="J111" s="52"/>
+      <c r="K111" s="52"/>
+      <c r="L111" s="52"/>
+    </row>
+    <row r="112" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A112" s="49"/>
+      <c r="B112" s="50"/>
+      <c r="C112" s="51"/>
+      <c r="E112" s="52"/>
+      <c r="F112" s="52"/>
+      <c r="G112" s="52"/>
+      <c r="H112" s="52"/>
+      <c r="I112" s="52"/>
+      <c r="J112" s="52"/>
+      <c r="K112" s="52"/>
+      <c r="L112" s="52"/>
+    </row>
+    <row r="113" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A113" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="B113" s="45" t="s">
+        <v>16</v>
+      </c>
+      <c r="C113" s="46" t="s">
         <v>51</v>
       </c>
-      <c r="E109" s="53">
-        <v>0.02</v>
-      </c>
-      <c r="F109" s="53"/>
-      <c r="G109" s="53"/>
-      <c r="H109" s="53"/>
-      <c r="I109" s="53"/>
-      <c r="J109" s="53"/>
-      <c r="K109" s="53"/>
-      <c r="L109" s="53"/>
-    </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A110" s="48" t="s">
-        <v>56</v>
-      </c>
-      <c r="B110" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="C110" s="49" t="s">
-        <v>51</v>
-      </c>
-      <c r="E110" s="53">
-        <v>0.03</v>
-      </c>
-      <c r="F110" s="53"/>
-      <c r="G110" s="53"/>
-      <c r="H110" s="53"/>
-      <c r="I110" s="53"/>
-      <c r="J110" s="53"/>
-      <c r="K110" s="53"/>
-      <c r="L110" s="53"/>
-    </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A111" s="48" t="s">
-        <v>57</v>
-      </c>
-      <c r="B111" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="C111" s="49" t="s">
-        <v>51</v>
-      </c>
-      <c r="E111" s="53">
-        <v>0.04</v>
-      </c>
-      <c r="F111" s="53"/>
-      <c r="G111" s="53"/>
-      <c r="H111" s="53"/>
-      <c r="I111" s="53"/>
-      <c r="J111" s="53"/>
-      <c r="K111" s="53"/>
-      <c r="L111" s="53"/>
-    </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A112" s="48" t="s">
-        <v>58</v>
-      </c>
-      <c r="B112" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="C112" s="49" t="s">
-        <v>51</v>
-      </c>
-      <c r="E112" s="53">
-        <v>0.05</v>
-      </c>
-      <c r="F112" s="53"/>
-      <c r="G112" s="53"/>
-      <c r="H112" s="53"/>
-      <c r="I112" s="53"/>
-      <c r="J112" s="53"/>
-      <c r="K112" s="53"/>
-      <c r="L112" s="53"/>
-    </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A113" s="48" t="s">
-        <v>59</v>
-      </c>
-      <c r="B113" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="C113" s="49" t="s">
-        <v>51</v>
-      </c>
-      <c r="E113" s="53">
-        <v>0.06</v>
-      </c>
-      <c r="F113" s="53"/>
-      <c r="G113" s="53"/>
-      <c r="H113" s="53"/>
-      <c r="I113" s="53"/>
-      <c r="J113" s="53"/>
-      <c r="K113" s="53"/>
-      <c r="L113" s="53"/>
+      <c r="E113" s="52">
+        <v>0</v>
+      </c>
+      <c r="F113" s="52"/>
+      <c r="G113" s="52"/>
+      <c r="H113" s="52"/>
+      <c r="I113" s="52"/>
+      <c r="J113" s="52"/>
+      <c r="K113" s="52"/>
+      <c r="L113" s="52"/>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A114" s="48" t="s">
-        <v>60</v>
+      <c r="A114" s="47" t="s">
+        <v>54</v>
       </c>
       <c r="B114" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="C114" s="49" t="s">
+      <c r="C114" s="48" t="s">
         <v>51</v>
       </c>
-      <c r="E114" s="53">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="F114" s="53"/>
-      <c r="G114" s="53"/>
-      <c r="H114" s="53"/>
-      <c r="I114" s="53"/>
-      <c r="J114" s="53"/>
-      <c r="K114" s="53"/>
-      <c r="L114" s="53"/>
+      <c r="E114" s="52">
+        <v>0.01</v>
+      </c>
+      <c r="F114" s="52"/>
+      <c r="G114" s="52"/>
+      <c r="H114" s="52"/>
+      <c r="I114" s="52"/>
+      <c r="J114" s="52"/>
+      <c r="K114" s="52"/>
+      <c r="L114" s="52"/>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A115" s="48" t="s">
-        <v>61</v>
+      <c r="A115" s="47" t="s">
+        <v>55</v>
       </c>
       <c r="B115" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="C115" s="49" t="s">
+      <c r="C115" s="48" t="s">
         <v>51</v>
       </c>
-      <c r="E115" s="53">
+      <c r="E115" s="52">
+        <v>0.02</v>
+      </c>
+      <c r="F115" s="52"/>
+      <c r="G115" s="52"/>
+      <c r="H115" s="52"/>
+      <c r="I115" s="52"/>
+      <c r="J115" s="52"/>
+      <c r="K115" s="52"/>
+      <c r="L115" s="52"/>
+    </row>
+    <row r="116" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A116" s="47" t="s">
+        <v>56</v>
+      </c>
+      <c r="B116" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="C116" s="48" t="s">
+        <v>51</v>
+      </c>
+      <c r="E116" s="52">
+        <v>0.03</v>
+      </c>
+      <c r="F116" s="52"/>
+      <c r="G116" s="52"/>
+      <c r="H116" s="52"/>
+      <c r="I116" s="52"/>
+      <c r="J116" s="52"/>
+      <c r="K116" s="52"/>
+      <c r="L116" s="52"/>
+    </row>
+    <row r="117" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A117" s="47" t="s">
+        <v>57</v>
+      </c>
+      <c r="B117" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="C117" s="48" t="s">
+        <v>51</v>
+      </c>
+      <c r="E117" s="52">
+        <v>0.04</v>
+      </c>
+      <c r="F117" s="52"/>
+      <c r="G117" s="52"/>
+      <c r="H117" s="52"/>
+      <c r="I117" s="52"/>
+      <c r="J117" s="52"/>
+      <c r="K117" s="52"/>
+      <c r="L117" s="52"/>
+    </row>
+    <row r="118" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A118" s="47" t="s">
+        <v>58</v>
+      </c>
+      <c r="B118" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="C118" s="48" t="s">
+        <v>51</v>
+      </c>
+      <c r="E118" s="52">
+        <v>0.05</v>
+      </c>
+      <c r="F118" s="52"/>
+      <c r="G118" s="52"/>
+      <c r="H118" s="52"/>
+      <c r="I118" s="52"/>
+      <c r="J118" s="52"/>
+      <c r="K118" s="52"/>
+      <c r="L118" s="52"/>
+    </row>
+    <row r="119" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A119" s="47" t="s">
+        <v>59</v>
+      </c>
+      <c r="B119" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="C119" s="48" t="s">
+        <v>51</v>
+      </c>
+      <c r="E119" s="52">
+        <v>0.06</v>
+      </c>
+      <c r="F119" s="52"/>
+      <c r="G119" s="52"/>
+      <c r="H119" s="52"/>
+      <c r="I119" s="52"/>
+      <c r="J119" s="52"/>
+      <c r="K119" s="52"/>
+      <c r="L119" s="52"/>
+    </row>
+    <row r="120" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A120" s="47" t="s">
+        <v>60</v>
+      </c>
+      <c r="B120" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="C120" s="48" t="s">
+        <v>51</v>
+      </c>
+      <c r="E120" s="52">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="F120" s="52"/>
+      <c r="G120" s="52"/>
+      <c r="H120" s="52"/>
+      <c r="I120" s="52"/>
+      <c r="J120" s="52"/>
+      <c r="K120" s="52"/>
+      <c r="L120" s="52"/>
+    </row>
+    <row r="121" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A121" s="47" t="s">
+        <v>61</v>
+      </c>
+      <c r="B121" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="C121" s="48" t="s">
+        <v>51</v>
+      </c>
+      <c r="E121" s="52">
         <v>0.08</v>
       </c>
-      <c r="F115" s="53"/>
-      <c r="G115" s="53"/>
-      <c r="H115" s="53"/>
-      <c r="I115" s="53"/>
-      <c r="J115" s="53"/>
-      <c r="K115" s="53"/>
-      <c r="L115" s="53"/>
-    </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A116" s="50" t="s">
+      <c r="F121" s="52"/>
+      <c r="G121" s="52"/>
+      <c r="H121" s="52"/>
+      <c r="I121" s="52"/>
+      <c r="J121" s="52"/>
+      <c r="K121" s="52"/>
+      <c r="L121" s="52"/>
+    </row>
+    <row r="122" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A122" s="49" t="s">
         <v>62</v>
       </c>
-      <c r="B116" s="51" t="s">
+      <c r="B122" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="C116" s="52" t="s">
+      <c r="C122" s="51" t="s">
         <v>52</v>
       </c>
-      <c r="E116" s="53">
+      <c r="E122" s="52">
         <v>100</v>
       </c>
-      <c r="F116" s="53"/>
-      <c r="G116" s="53"/>
-      <c r="H116" s="53"/>
-      <c r="I116" s="53"/>
-      <c r="J116" s="53"/>
-      <c r="K116" s="53"/>
-      <c r="L116" s="53"/>
-    </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A117" s="48"/>
-      <c r="C117" s="49"/>
-      <c r="E117" s="54"/>
+      <c r="F122" s="52"/>
+      <c r="G122" s="52"/>
+      <c r="H122" s="52"/>
+      <c r="I122" s="52"/>
+      <c r="J122" s="52"/>
+      <c r="K122" s="52"/>
+      <c r="L122" s="52"/>
+    </row>
+    <row r="123" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A123" s="47"/>
+      <c r="C123" s="48"/>
+      <c r="E123" s="53"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -9090,79 +9221,79 @@
       </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B5" s="96" t="s">
+      <c r="B5" s="92" t="s">
         <v>182</v>
       </c>
-      <c r="C5" s="96" t="s">
+      <c r="C5" s="92" t="s">
         <v>180</v>
       </c>
-      <c r="D5" s="95" t="s">
+      <c r="D5" s="91" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B6" s="97" t="s">
+      <c r="B6" s="93" t="s">
         <v>183</v>
       </c>
-      <c r="C6" s="99" t="s">
+      <c r="C6" s="95" t="s">
         <v>51</v>
       </c>
-      <c r="D6" s="53">
+      <c r="D6" s="52">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B7" s="97" t="s">
+      <c r="B7" s="93" t="s">
         <v>184</v>
       </c>
-      <c r="C7" s="99" t="s">
+      <c r="C7" s="95" t="s">
         <v>51</v>
       </c>
-      <c r="D7" s="53">
+      <c r="D7" s="52">
         <v>0.01</v>
       </c>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B8" s="97" t="s">
+      <c r="B8" s="93" t="s">
         <v>185</v>
       </c>
-      <c r="C8" s="99" t="s">
+      <c r="C8" s="95" t="s">
         <v>51</v>
       </c>
-      <c r="D8" s="53">
+      <c r="D8" s="52">
         <v>0.02</v>
       </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B9" s="97" t="s">
+      <c r="B9" s="93" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="99" t="s">
+      <c r="C9" s="95" t="s">
         <v>51</v>
       </c>
-      <c r="D9" s="53">
+      <c r="D9" s="52">
         <v>0.03</v>
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B10" s="97" t="s">
+      <c r="B10" s="93" t="s">
         <v>186</v>
       </c>
-      <c r="C10" s="99" t="s">
+      <c r="C10" s="95" t="s">
         <v>51</v>
       </c>
-      <c r="D10" s="53">
+      <c r="D10" s="52">
         <v>0.04</v>
       </c>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B11" s="97" t="s">
+      <c r="B11" s="93" t="s">
         <v>187</v>
       </c>
-      <c r="C11" s="99" t="s">
+      <c r="C11" s="95" t="s">
         <v>51</v>
       </c>
-      <c r="D11" s="53">
+      <c r="D11" s="52">
         <v>0.05</v>
       </c>
       <c r="F11" t="s">
@@ -9170,46 +9301,46 @@
       </c>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B12" s="97" t="s">
+      <c r="B12" s="93" t="s">
         <v>188</v>
       </c>
-      <c r="C12" s="99" t="s">
+      <c r="C12" s="95" t="s">
         <v>51</v>
       </c>
-      <c r="D12" s="53">
+      <c r="D12" s="52">
         <v>0.06</v>
       </c>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B13" s="97" t="s">
+      <c r="B13" s="93" t="s">
         <v>189</v>
       </c>
-      <c r="C13" s="99" t="s">
+      <c r="C13" s="95" t="s">
         <v>51</v>
       </c>
-      <c r="D13" s="53">
+      <c r="D13" s="52">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B14" s="97" t="s">
+      <c r="B14" s="93" t="s">
         <v>190</v>
       </c>
-      <c r="C14" s="99" t="s">
+      <c r="C14" s="95" t="s">
         <v>51</v>
       </c>
-      <c r="D14" s="53">
+      <c r="D14" s="52">
         <v>0.08</v>
       </c>
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B15" s="98" t="s">
+      <c r="B15" s="94" t="s">
         <v>191</v>
       </c>
-      <c r="C15" s="100" t="s">
+      <c r="C15" s="96" t="s">
         <v>52</v>
       </c>
-      <c r="D15" s="53">
+      <c r="D15" s="52">
         <v>100</v>
       </c>
     </row>
